--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25christentum/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A2DDD6-D30E-214D-9620-6D403A5ED174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E62DC8-35AB-8647-ADEB-1743413A55C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -370,15 +370,9 @@
     <t xml:space="preserve">In der Primärquelle: Eine Person in jeder von 3 Etappen (1. Apostel, 2. Nachfolger der Apostel, 3. Neue) identifizieren. </t>
   </si>
   <si>
-    <t>Aphrahat</t>
-  </si>
-  <si>
     <t>Was wird mit wem gefeiert?</t>
   </si>
   <si>
-    <t xml:space="preserve">Das des nächsten Ostern nach Aphrahats Vorgaben rechnen. </t>
-  </si>
-  <si>
     <t>Bauer vs. Stark; Ephrem</t>
   </si>
   <si>
@@ -500,6 +494,12 @@
   </si>
   <si>
     <t>deutschebibelgesellschaftApostelgeschichte12Lutherbibel</t>
+  </si>
+  <si>
+    <t>aphrahat12UeberPascha1991, yuvalEasterPassoverEarly1999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Das Datum des nächsten Ostern nach den Quartodecimans bzw. nach Aphrahats Vorgaben rechnen. </t>
   </si>
 </sst>
 </file>
@@ -1000,7 +1000,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>14</v>
@@ -1051,7 +1051,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>19</v>
@@ -1066,7 +1066,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L2" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B2 &amp; ". " &amp; F2,".",""),"&amp;","")," ","-"),"--","-")</f>
@@ -1126,14 +1126,14 @@
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L3" t="str">
         <f t="shared" ref="L3:L14" si="5">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B3 &amp; ". " &amp; F3,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>2-Heilige-Schriften-und-die-apostolische-Tradition</v>
       </c>
       <c r="M3" s="18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N3" t="s">
         <v>40</v>
@@ -1170,10 +1170,10 @@
         <v>31</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H4" t="s">
         <v>28</v>
@@ -1187,20 +1187,20 @@
         <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L4" t="str">
         <f t="shared" si="5"/>
         <v>3-Abendmahl,-Pessach-und-Ostern</v>
       </c>
       <c r="M4" s="16" t="s">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="N4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O4" t="s">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="P4" t="str">
         <f t="shared" si="2"/>
@@ -1252,13 +1252,13 @@
         <v>4-Orthodoxie-und-Häresie</v>
       </c>
       <c r="M5" s="16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
+        <v>44</v>
+      </c>
+      <c r="O5" t="s">
         <v>46</v>
-      </c>
-      <c r="O5" t="s">
-        <v>48</v>
       </c>
       <c r="P5" t="str">
         <f t="shared" si="2"/>
@@ -1306,20 +1306,20 @@
         <v>5</v>
       </c>
       <c r="K6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L6" t="str">
         <f t="shared" si="5"/>
         <v>5-Askese,-Martyrium,-Wunder-und-Wallfahrt</v>
       </c>
       <c r="M6" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="N6" t="s">
+        <v>48</v>
+      </c>
+      <c r="O6" t="s">
         <v>49</v>
-      </c>
-      <c r="N6" t="s">
-        <v>50</v>
-      </c>
-      <c r="O6" t="s">
-        <v>51</v>
       </c>
       <c r="P6" t="str">
         <f t="shared" si="2"/>
@@ -1353,7 +1353,7 @@
         <v>21</v>
       </c>
       <c r="G7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="4"/>
@@ -1368,10 +1368,10 @@
         <v>6-Exkursion</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="P7" t="str">
         <f t="shared" si="2"/>
@@ -1421,10 +1421,10 @@
         <v>32</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I9" t="str">
         <f t="shared" si="4"/>
@@ -1435,7 +1435,7 @@
         <v>7</v>
       </c>
       <c r="K9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L9" t="str">
         <f t="shared" si="5"/>
@@ -1445,10 +1445,10 @@
         <v>33</v>
       </c>
       <c r="N9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="P9" t="str">
         <f t="shared" si="2"/>
@@ -1479,10 +1479,10 @@
         <v>32</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I10" t="str">
         <f t="shared" si="4"/>
@@ -1497,13 +1497,13 @@
         <v>8-Kirche-des-Ostens-(ostsyrisch/assyrianisch)</v>
       </c>
       <c r="M10" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O10" t="s">
         <v>57</v>
-      </c>
-      <c r="N10" t="s">
-        <v>58</v>
-      </c>
-      <c r="O10" t="s">
-        <v>59</v>
       </c>
       <c r="P10" t="str">
         <f t="shared" si="2"/>
@@ -1534,10 +1534,10 @@
         <v>32</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I11" t="str">
         <f t="shared" si="4"/>
@@ -1552,13 +1552,13 @@
         <v>9-Kopten-und-Syrisch-Orthodoxen</v>
       </c>
       <c r="M11" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N11" t="s">
+        <v>59</v>
+      </c>
+      <c r="O11" t="s">
         <v>60</v>
-      </c>
-      <c r="N11" t="s">
-        <v>61</v>
-      </c>
-      <c r="O11" t="s">
-        <v>62</v>
       </c>
       <c r="P11" t="str">
         <f t="shared" si="2"/>
@@ -1608,10 +1608,10 @@
         <v>32</v>
       </c>
       <c r="F13" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" t="s">
         <v>73</v>
-      </c>
-      <c r="G13" t="s">
-        <v>75</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="4"/>
@@ -1622,20 +1622,20 @@
         <v>10</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="L13" t="str">
         <f t="shared" si="5"/>
         <v>10-Armenier-und-Äthiopier</v>
       </c>
       <c r="M13" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N13" t="s">
+        <v>62</v>
+      </c>
+      <c r="O13" t="s">
         <v>63</v>
-      </c>
-      <c r="N13" t="s">
-        <v>64</v>
-      </c>
-      <c r="O13" t="s">
-        <v>65</v>
       </c>
       <c r="P13" t="str">
         <f t="shared" si="2"/>
@@ -1685,10 +1685,10 @@
       </c>
       <c r="M14" s="9"/>
       <c r="N14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="O14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="P14" t="str">
         <f t="shared" si="2"/>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25christentum/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E62DC8-35AB-8647-ADEB-1743413A55C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EEFAF54-203F-1840-8276-F68554D46808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -241,7 +241,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="91">
   <si>
     <t>blank</t>
   </si>
@@ -500,6 +500,21 @@
   </si>
   <si>
     <t xml:space="preserve">Das Datum des nächsten Ostern nach den Quartodecimans bzw. nach Aphrahats Vorgaben rechnen. </t>
+  </si>
+  <si>
+    <t>slide-frontmatter</t>
+  </si>
+  <si>
+    <t>slide-body1</t>
+  </si>
+  <si>
+    <t>slide-body2</t>
+  </si>
+  <si>
+    <t>slide-content</t>
+  </si>
+  <si>
+    <t>slide-filename</t>
   </si>
 </sst>
 </file>
@@ -614,7 +629,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -656,6 +671,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -962,7 +980,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" hidden="1" customWidth="1"/>
@@ -980,10 +998,11 @@
     <col min="13" max="13" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="77.83203125" customWidth="1"/>
     <col min="16" max="16" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.5" customWidth="1"/>
+    <col min="17" max="18" width="32.5" customWidth="1"/>
+    <col min="19" max="19" width="39.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1035,8 +1054,23 @@
       <c r="Q1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="R1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="S1" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="T1" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="U1" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="V1" s="19" t="s">
+        <v>89</v>
+      </c>
     </row>
-    <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -1093,8 +1127,105 @@
 level: overview
 ---</v>
       </c>
+      <c r="R2" t="str">
+        <f>_xlfn.REGEXREPLACE(D2,"\.md","-slides.md")</f>
+        <v>2025-04-28-1-slides.md</v>
+      </c>
+      <c r="S2" t="str">
+        <f>"---
+layout: reveal
+title: '"&amp;G2&amp;"'
+author: 'Nathan Gibson'
+session: "&amp;B2&amp;"
+tags: ["&amp;B2&amp;",slides]
+category: slides
+image: "&amp;K2&amp;"
+parallaxBackgroundImage: 'assets/img/"&amp;K2&amp;"'
+---
+"</f>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Ist das Christentum eine westliche Religion?'
+author: 'Nathan Gibson'
+session: 1
+tags: [1,slides]
+category: slides
+image: good-friday-aleppo.jpg
+parallaxBackgroundImage: 'assets/img/good-friday-aleppo.jpg'
+---
+</v>
+      </c>
+      <c r="T2" t="str">
+        <f>"# Einführung ins Christentum
+{: .r-fit-text}
+### "&amp;G2&amp;"
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+"&amp;N1&amp;"
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+"&amp;N2</f>
+        <v># Einführung ins Christentum
+{: .r-fit-text}
+### Ist das Christentum eine westliche Religion?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+objective
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+1. Eigene Ziele im Kurs setzen.
+2. Westliche Vorstellungen des Christentums erstmal hinterfragen.</v>
+      </c>
+      <c r="U2" t="str">
+        <f>"
+## Lektüre
+## Diskussion
+## Vorschau
+"&amp;G3</f>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+Wie wird die christliche Botschaft idealerweise vermittelt?</v>
+      </c>
+      <c r="V2" t="str">
+        <f>_xlfn.CONCAT(S2:U2)</f>
+        <v>---
+layout: reveal
+title: 'Ist das Christentum eine westliche Religion?'
+author: 'Nathan Gibson'
+session: 1
+tags: [1,slides]
+category: slides
+image: good-friday-aleppo.jpg
+parallaxBackgroundImage: 'assets/img/good-friday-aleppo.jpg'
+---
+# Einführung ins Christentum
+{: .r-fit-text}
+### Ist das Christentum eine westliche Religion?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+objective
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+1. Eigene Ziele im Kurs setzen.
+2. Westliche Vorstellungen des Christentums erstmal hinterfragen.
+## Lektüre
+## Diskussion
+## Vorschau
+Wie wird die christliche Botschaft idealerweise vermittelt?</v>
+      </c>
     </row>
-    <row r="3" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="3">
         <v>2</v>
       </c>
@@ -1154,8 +1285,105 @@
 level: overview
 ---</v>
       </c>
+      <c r="R3" t="str">
+        <f t="shared" ref="R3:R14" si="6">_xlfn.REGEXREPLACE(D3,"\.md","-slides.md")</f>
+        <v>2025-05-05-2-slides.md</v>
+      </c>
+      <c r="S3" t="str">
+        <f t="shared" ref="S3:S14" si="7">"---
+layout: reveal
+title: '"&amp;G3&amp;"'
+author: 'Nathan Gibson'
+session: "&amp;B3&amp;"
+tags: ["&amp;B3&amp;",slides]
+category: slides
+image: "&amp;K3&amp;"
+parallaxBackgroundImage: 'assets/img/"&amp;K3&amp;"'
+---
+"</f>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Wie wird die christliche Botschaft idealerweise vermittelt?'
+author: 'Nathan Gibson'
+session: 2
+tags: [2,slides]
+category: slides
+image: ihlara-valley-cappadocia.jpg
+parallaxBackgroundImage: 'assets/img/ihlara-valley-cappadocia.jpg'
+---
+</v>
+      </c>
+      <c r="T3" t="str">
+        <f t="shared" ref="T3:T14" si="8">"# Einführung ins Christentum
+{: .r-fit-text}
+### "&amp;G3&amp;"
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+"&amp;N2&amp;"
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+"&amp;N3</f>
+        <v xml:space="preserve"># Einführung ins Christentum
+{: .r-fit-text}
+### Wie wird die christliche Botschaft idealerweise vermittelt?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+1. Eigene Ziele im Kurs setzen.
+2. Westliche Vorstellungen des Christentums erstmal hinterfragen.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Die Rolle der schriftlichen und mündlichen "apostolischen" Traditionen im frühchristlichen Selbstverständnis skizzieren können. </v>
+      </c>
+      <c r="U3" t="str">
+        <f t="shared" ref="U3:U14" si="9">"
+## Lektüre
+## Diskussion
+## Vorschau
+"&amp;G4</f>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+Was wird mit wem gefeiert?</v>
+      </c>
+      <c r="V3" t="str">
+        <f t="shared" ref="V3:V14" si="10">_xlfn.CONCAT(S3:U3)</f>
+        <v>---
+layout: reveal
+title: 'Wie wird die christliche Botschaft idealerweise vermittelt?'
+author: 'Nathan Gibson'
+session: 2
+tags: [2,slides]
+category: slides
+image: ihlara-valley-cappadocia.jpg
+parallaxBackgroundImage: 'assets/img/ihlara-valley-cappadocia.jpg'
+---
+# Einführung ins Christentum
+{: .r-fit-text}
+### Wie wird die christliche Botschaft idealerweise vermittelt?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+1. Eigene Ziele im Kurs setzen.
+2. Westliche Vorstellungen des Christentums erstmal hinterfragen.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Die Rolle der schriftlichen und mündlichen "apostolischen" Traditionen im frühchristlichen Selbstverständnis skizzieren können. 
+## Lektüre
+## Diskussion
+## Vorschau
+Was wird mit wem gefeiert?</v>
+      </c>
     </row>
-    <row r="4" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="3">
         <v>3</v>
       </c>
@@ -1215,8 +1443,78 @@
 level: overview
 ---</v>
       </c>
+      <c r="R4" t="str">
+        <f t="shared" si="6"/>
+        <v>2025-05-12-3-slides.md</v>
+      </c>
+      <c r="S4" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Was wird mit wem gefeiert?'
+author: 'Nathan Gibson'
+session: 3
+tags: [3,slides]
+category: slides
+image: seder.jpg
+parallaxBackgroundImage: 'assets/img/seder.jpg'
+---
+</v>
+      </c>
+      <c r="T4" t="str">
+        <f t="shared" si="8"/>
+        <v># Einführung ins Christentum
+{: .r-fit-text}
+### Was wird mit wem gefeiert?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Die Rolle der schriftlichen und mündlichen "apostolischen" Traditionen im frühchristlichen Selbstverständnis skizzieren können. 
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Hybridität und Selbstpositionierung zwischen jüdischen Gemeinden und Jesu Nachfolger anhand von Ritualen illustrieren können.</v>
+      </c>
+      <c r="U4" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+Warum ist es wichtig, richtig zu glauben?</v>
+      </c>
+      <c r="V4" t="str">
+        <f t="shared" si="10"/>
+        <v>---
+layout: reveal
+title: 'Was wird mit wem gefeiert?'
+author: 'Nathan Gibson'
+session: 3
+tags: [3,slides]
+category: slides
+image: seder.jpg
+parallaxBackgroundImage: 'assets/img/seder.jpg'
+---
+# Einführung ins Christentum
+{: .r-fit-text}
+### Was wird mit wem gefeiert?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Die Rolle der schriftlichen und mündlichen "apostolischen" Traditionen im frühchristlichen Selbstverständnis skizzieren können. 
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Hybridität und Selbstpositionierung zwischen jüdischen Gemeinden und Jesu Nachfolger anhand von Ritualen illustrieren können.
+## Lektüre
+## Diskussion
+## Vorschau
+Warum ist es wichtig, richtig zu glauben?</v>
+      </c>
     </row>
-    <row r="5" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="3">
         <v>4</v>
       </c>
@@ -1273,8 +1571,78 @@
 level: overview
 ---</v>
       </c>
+      <c r="R5" t="str">
+        <f t="shared" si="6"/>
+        <v>2025-05-19-4-slides.md</v>
+      </c>
+      <c r="S5" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Warum ist es wichtig, richtig zu glauben?'
+author: 'Nathan Gibson'
+session: 4
+tags: [4,slides]
+category: slides
+image: 
+parallaxBackgroundImage: 'assets/img/'
+---
+</v>
+      </c>
+      <c r="T5" t="str">
+        <f t="shared" si="8"/>
+        <v># Einführung ins Christentum
+{: .r-fit-text}
+### Warum ist es wichtig, richtig zu glauben?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Hybridität und Selbstpositionierung zwischen jüdischen Gemeinden und Jesu Nachfolger anhand von Ritualen illustrieren können.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Sowohl die innere Logik der orthodoxischen Erzählung als auch historisch-kritische Bemerkungen daran erklären können.</v>
+      </c>
+      <c r="U5" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+Wer und was ist heilig?</v>
+      </c>
+      <c r="V5" t="str">
+        <f t="shared" si="10"/>
+        <v>---
+layout: reveal
+title: 'Warum ist es wichtig, richtig zu glauben?'
+author: 'Nathan Gibson'
+session: 4
+tags: [4,slides]
+category: slides
+image: 
+parallaxBackgroundImage: 'assets/img/'
+---
+# Einführung ins Christentum
+{: .r-fit-text}
+### Warum ist es wichtig, richtig zu glauben?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Hybridität und Selbstpositionierung zwischen jüdischen Gemeinden und Jesu Nachfolger anhand von Ritualen illustrieren können.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Sowohl die innere Logik der orthodoxischen Erzählung als auch historisch-kritische Bemerkungen daran erklären können.
+## Lektüre
+## Diskussion
+## Vorschau
+Wer und was ist heilig?</v>
+      </c>
     </row>
-    <row r="6" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="3">
         <v>5</v>
       </c>
@@ -1334,8 +1702,78 @@
 level: overview
 ---</v>
       </c>
+      <c r="R6" t="str">
+        <f t="shared" si="6"/>
+        <v>2025-05-26-5-slides.md</v>
+      </c>
+      <c r="S6" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Wer und was ist heilig?'
+author: 'Nathan Gibson'
+session: 5
+tags: [5,slides]
+category: slides
+image: aksehir-red-church-cappadocia.jpg
+parallaxBackgroundImage: 'assets/img/aksehir-red-church-cappadocia.jpg'
+---
+</v>
+      </c>
+      <c r="T6" t="str">
+        <f t="shared" si="8"/>
+        <v># Einführung ins Christentum
+{: .r-fit-text}
+### Wer und was ist heilig?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Sowohl die innere Logik der orthodoxischen Erzählung als auch historisch-kritische Bemerkungen daran erklären können.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Den Heiligkeitsbegriff mit Beispielen erklären können.</v>
+      </c>
+      <c r="U6" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+Wie sieht eine Kirche aus?</v>
+      </c>
+      <c r="V6" t="str">
+        <f t="shared" si="10"/>
+        <v>---
+layout: reveal
+title: 'Wer und was ist heilig?'
+author: 'Nathan Gibson'
+session: 5
+tags: [5,slides]
+category: slides
+image: aksehir-red-church-cappadocia.jpg
+parallaxBackgroundImage: 'assets/img/aksehir-red-church-cappadocia.jpg'
+---
+# Einführung ins Christentum
+{: .r-fit-text}
+### Wer und was ist heilig?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Sowohl die innere Logik der orthodoxischen Erzählung als auch historisch-kritische Bemerkungen daran erklären können.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Den Heiligkeitsbegriff mit Beispielen erklären können.
+## Lektüre
+## Diskussion
+## Vorschau
+Wie sieht eine Kirche aus?</v>
+      </c>
     </row>
-    <row r="7" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="3">
         <v>6</v>
       </c>
@@ -1386,8 +1824,78 @@
 level: overview
 ---</v>
       </c>
+      <c r="R7" t="str">
+        <f t="shared" si="6"/>
+        <v>2025-06-02-6-slides.md</v>
+      </c>
+      <c r="S7" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Wie sieht eine Kirche aus?'
+author: 'Nathan Gibson'
+session: 6
+tags: [6,slides]
+category: slides
+image: 
+parallaxBackgroundImage: 'assets/img/'
+---
+</v>
+      </c>
+      <c r="T7" t="str">
+        <f t="shared" si="8"/>
+        <v># Einführung ins Christentum
+{: .r-fit-text}
+### Wie sieht eine Kirche aus?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Den Heiligkeitsbegriff mit Beispielen erklären können.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Erfahren, wie in einer nicht-westlichen Tradition einen Gottesdienst gefeiert wird.</v>
+      </c>
+      <c r="U7" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+</v>
+      </c>
+      <c r="V7" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Wie sieht eine Kirche aus?'
+author: 'Nathan Gibson'
+session: 6
+tags: [6,slides]
+category: slides
+image: 
+parallaxBackgroundImage: 'assets/img/'
+---
+# Einführung ins Christentum
+{: .r-fit-text}
+### Wie sieht eine Kirche aus?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Den Heiligkeitsbegriff mit Beispielen erklären können.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Erfahren, wie in einer nicht-westlichen Tradition einen Gottesdienst gefeiert wird.
+## Lektüre
+## Diskussion
+## Vorschau
+</v>
+      </c>
     </row>
-    <row r="8" spans="1:17" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="12"/>
       <c r="C8" s="13">
         <v>45817</v>
@@ -1405,8 +1913,77 @@
       </c>
       <c r="J8" s="12"/>
       <c r="M8" s="15"/>
+      <c r="R8" t="str">
+        <f t="shared" si="6"/>
+        <v>2025-06-09-pfingstmontag-slides.md</v>
+      </c>
+      <c r="S8" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: ''
+author: 'Nathan Gibson'
+session: 
+tags: [,slides]
+category: slides
+image: 
+parallaxBackgroundImage: 'assets/img/'
+---
+</v>
+      </c>
+      <c r="T8" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve"># Einführung ins Christentum
+{: .r-fit-text}
+### 
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Erfahren, wie in einer nicht-westlichen Tradition einen Gottesdienst gefeiert wird.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+</v>
+      </c>
+      <c r="U8" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+Wie verstanden sich Christen und Muslime?</v>
+      </c>
+      <c r="V8" t="str">
+        <f t="shared" si="10"/>
+        <v>---
+layout: reveal
+title: ''
+author: 'Nathan Gibson'
+session: 
+tags: [,slides]
+category: slides
+image: 
+parallaxBackgroundImage: 'assets/img/'
+---
+# Einführung ins Christentum
+{: .r-fit-text}
+### 
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Erfahren, wie in einer nicht-westlichen Tradition einen Gottesdienst gefeiert wird.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+## Lektüre
+## Diskussion
+## Vorschau
+Wie verstanden sich Christen und Muslime?</v>
+      </c>
     </row>
-    <row r="9" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="3">
         <v>7</v>
       </c>
@@ -1463,8 +2040,76 @@
 level: overview
 ---</v>
       </c>
+      <c r="R9" t="str">
+        <f t="shared" si="6"/>
+        <v>2025-06-16-7-slides.md</v>
+      </c>
+      <c r="S9" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Wie verstanden sich Christen und Muslime?'
+author: 'Nathan Gibson'
+session: 7
+tags: [7,slides]
+category: slides
+image: st-paul-harissa.jpg
+parallaxBackgroundImage: 'assets/img/st-paul-harissa.jpg'
+---
+</v>
+      </c>
+      <c r="T9" t="str">
+        <f t="shared" si="8"/>
+        <v># Einführung ins Christentum
+{: .r-fit-text}
+### Wie verstanden sich Christen und Muslime?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Einige Bereiche nennen können, in denen der langjährige Austausch zwischen islamischen und ostkirchlichen Gemeinschaften besonders bedeutsam war.</v>
+      </c>
+      <c r="U9" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (I)</v>
+      </c>
+      <c r="V9" t="str">
+        <f t="shared" si="10"/>
+        <v>---
+layout: reveal
+title: 'Wie verstanden sich Christen und Muslime?'
+author: 'Nathan Gibson'
+session: 7
+tags: [7,slides]
+category: slides
+image: st-paul-harissa.jpg
+parallaxBackgroundImage: 'assets/img/st-paul-harissa.jpg'
+---
+# Einführung ins Christentum
+{: .r-fit-text}
+### Wie verstanden sich Christen und Muslime?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Einige Bereiche nennen können, in denen der langjährige Austausch zwischen islamischen und ostkirchlichen Gemeinschaften besonders bedeutsam war.
+## Lektüre
+## Diskussion
+## Vorschau
+Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (I)</v>
+      </c>
     </row>
-    <row r="10" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="3">
         <v>8</v>
       </c>
@@ -1518,8 +2163,78 @@
 level: overview
 ---</v>
       </c>
+      <c r="R10" t="str">
+        <f t="shared" si="6"/>
+        <v>2025-06-23-8-slides.md</v>
+      </c>
+      <c r="S10" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (I)'
+author: 'Nathan Gibson'
+session: 8
+tags: [8,slides]
+category: slides
+image: 
+parallaxBackgroundImage: 'assets/img/'
+---
+</v>
+      </c>
+      <c r="T10" t="str">
+        <f t="shared" si="8"/>
+        <v># Einführung ins Christentum
+{: .r-fit-text}
+### Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (I)
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Einige Bereiche nennen können, in denen der langjährige Austausch zwischen islamischen und ostkirchlichen Gemeinschaften besonders bedeutsam war.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Die größten Gemeinsamkeiten und Unterschiede zwischen der Kirche des Ostens und den griechischen oder römischen Kirchen identifizieren.</v>
+      </c>
+      <c r="U10" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+Wie entfalteten sich die einheimischen Kirchen innerhalb des Römischen Reiches? </v>
+      </c>
+      <c r="V10" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (I)'
+author: 'Nathan Gibson'
+session: 8
+tags: [8,slides]
+category: slides
+image: 
+parallaxBackgroundImage: 'assets/img/'
+---
+# Einführung ins Christentum
+{: .r-fit-text}
+### Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (I)
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Einige Bereiche nennen können, in denen der langjährige Austausch zwischen islamischen und ostkirchlichen Gemeinschaften besonders bedeutsam war.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Die größten Gemeinsamkeiten und Unterschiede zwischen der Kirche des Ostens und den griechischen oder römischen Kirchen identifizieren.
+## Lektüre
+## Diskussion
+## Vorschau
+Wie entfalteten sich die einheimischen Kirchen innerhalb des Römischen Reiches? </v>
+      </c>
     </row>
-    <row r="11" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="3">
         <v>9</v>
       </c>
@@ -1573,8 +2288,78 @@
 level: overview
 ---</v>
       </c>
+      <c r="R11" t="str">
+        <f t="shared" si="6"/>
+        <v>2025-06-30-9-slides.md</v>
+      </c>
+      <c r="S11" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Wie entfalteten sich die einheimischen Kirchen innerhalb des Römischen Reiches? '
+author: 'Nathan Gibson'
+session: 9
+tags: [9,slides]
+category: slides
+image: 
+parallaxBackgroundImage: 'assets/img/'
+---
+</v>
+      </c>
+      <c r="T11" t="str">
+        <f t="shared" si="8"/>
+        <v># Einführung ins Christentum
+{: .r-fit-text}
+### Wie entfalteten sich die einheimischen Kirchen innerhalb des Römischen Reiches? 
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Die größten Gemeinsamkeiten und Unterschiede zwischen der Kirche des Ostens und den griechischen oder römischen Kirchen identifizieren.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Einige Aspekte der Identitätserzählung der koptischen und syrisch-orthodoxischen Gemeinden zusammenfassen können.</v>
+      </c>
+      <c r="U11" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+</v>
+      </c>
+      <c r="V11" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Wie entfalteten sich die einheimischen Kirchen innerhalb des Römischen Reiches? '
+author: 'Nathan Gibson'
+session: 9
+tags: [9,slides]
+category: slides
+image: 
+parallaxBackgroundImage: 'assets/img/'
+---
+# Einführung ins Christentum
+{: .r-fit-text}
+### Wie entfalteten sich die einheimischen Kirchen innerhalb des Römischen Reiches? 
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Die größten Gemeinsamkeiten und Unterschiede zwischen der Kirche des Ostens und den griechischen oder römischen Kirchen identifizieren.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Einige Aspekte der Identitätserzählung der koptischen und syrisch-orthodoxischen Gemeinden zusammenfassen können.
+## Lektüre
+## Diskussion
+## Vorschau
+</v>
+      </c>
     </row>
-    <row r="12" spans="1:17" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="12"/>
       <c r="C12" s="13">
         <v>45845</v>
@@ -1592,8 +2377,77 @@
       </c>
       <c r="J12" s="12"/>
       <c r="M12" s="15"/>
+      <c r="R12" t="str">
+        <f t="shared" si="6"/>
+        <v>2025-06-09-sommerfest-slides.md</v>
+      </c>
+      <c r="S12" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: ''
+author: 'Nathan Gibson'
+session: 
+tags: [,slides]
+category: slides
+image: 
+parallaxBackgroundImage: 'assets/img/'
+---
+</v>
+      </c>
+      <c r="T12" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve"># Einführung ins Christentum
+{: .r-fit-text}
+### 
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Einige Aspekte der Identitätserzählung der koptischen und syrisch-orthodoxischen Gemeinden zusammenfassen können.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+</v>
+      </c>
+      <c r="U12" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (II)</v>
+      </c>
+      <c r="V12" t="str">
+        <f t="shared" si="10"/>
+        <v>---
+layout: reveal
+title: ''
+author: 'Nathan Gibson'
+session: 
+tags: [,slides]
+category: slides
+image: 
+parallaxBackgroundImage: 'assets/img/'
+---
+# Einführung ins Christentum
+{: .r-fit-text}
+### 
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Einige Aspekte der Identitätserzählung der koptischen und syrisch-orthodoxischen Gemeinden zusammenfassen können.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+## Lektüre
+## Diskussion
+## Vorschau
+Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (II)</v>
+      </c>
     </row>
-    <row r="13" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="3">
         <v>10</v>
       </c>
@@ -1650,8 +2504,76 @@
 level: overview
 ---</v>
       </c>
+      <c r="R13" t="str">
+        <f t="shared" si="6"/>
+        <v>2025-07-14-10-slides.md</v>
+      </c>
+      <c r="S13" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (II)'
+author: 'Nathan Gibson'
+session: 10
+tags: [10,slides]
+category: slides
+image: armenian-bell.jpg
+parallaxBackgroundImage: 'assets/img/armenian-bell.jpg'
+---
+</v>
+      </c>
+      <c r="T13" t="str">
+        <f t="shared" si="8"/>
+        <v># Einführung ins Christentum
+{: .r-fit-text}
+### Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (II)
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Eckpunkte der armenischen und äthiopischen Selbstnarrativen erzählen können.</v>
+      </c>
+      <c r="U13" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+Was haben wir gelernt?</v>
+      </c>
+      <c r="V13" t="str">
+        <f t="shared" si="10"/>
+        <v>---
+layout: reveal
+title: 'Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (II)'
+author: 'Nathan Gibson'
+session: 10
+tags: [10,slides]
+category: slides
+image: armenian-bell.jpg
+parallaxBackgroundImage: 'assets/img/armenian-bell.jpg'
+---
+# Einführung ins Christentum
+{: .r-fit-text}
+### Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (II)
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Eckpunkte der armenischen und äthiopischen Selbstnarrativen erzählen können.
+## Lektüre
+## Diskussion
+## Vorschau
+Was haben wir gelernt?</v>
+      </c>
     </row>
-    <row r="14" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="3">
         <v>11</v>
       </c>
@@ -1703,11 +2625,81 @@
 level: overview
 ---</v>
       </c>
+      <c r="R14" t="str">
+        <f t="shared" si="6"/>
+        <v>2025-07-21-11-slides.md</v>
+      </c>
+      <c r="S14" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Was haben wir gelernt?'
+author: 'Nathan Gibson'
+session: 11
+tags: [11,slides]
+category: slides
+image: 
+parallaxBackgroundImage: 'assets/img/'
+---
+</v>
+      </c>
+      <c r="T14" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve"># Einführung ins Christentum
+{: .r-fit-text}
+### Was haben wir gelernt?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Eckpunkte der armenischen und äthiopischen Selbstnarrativen erzählen können.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Über die Kursinhalte reflektieren und das eingeworbene Wissen für sich versichern. </v>
+      </c>
+      <c r="U14" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+</v>
+      </c>
+      <c r="V14" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Was haben wir gelernt?'
+author: 'Nathan Gibson'
+session: 11
+tags: [11,slides]
+category: slides
+image: 
+parallaxBackgroundImage: 'assets/img/'
+---
+# Einführung ins Christentum
+{: .r-fit-text}
+### Was haben wir gelernt?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Eckpunkte der armenischen und äthiopischen Selbstnarrativen erzählen können.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Über die Kursinhalte reflektieren und das eingeworbene Wissen für sich versichern. 
+## Lektüre
+## Diskussion
+## Vorschau
+</v>
+      </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="E16" s="4"/>
     </row>
   </sheetData>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25christentum/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EEFAF54-203F-1840-8276-F68554D46808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7725BDF1-1E78-344B-82A7-DA359F159DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -629,7 +629,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -671,9 +671,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -989,7 +986,7 @@
     <col min="4" max="4" width="15.33203125" style="6" customWidth="1"/>
     <col min="5" max="5" width="26.83203125" customWidth="1"/>
     <col min="6" max="6" width="39" customWidth="1"/>
-    <col min="7" max="7" width="60.83203125" customWidth="1"/>
+    <col min="7" max="7" width="35.1640625" customWidth="1"/>
     <col min="8" max="8" width="61" customWidth="1"/>
     <col min="9" max="9" width="27.1640625" customWidth="1"/>
     <col min="10" max="10" width="13.1640625" style="5" bestFit="1" customWidth="1"/>
@@ -1057,16 +1054,16 @@
       <c r="R1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="S1" s="19" t="s">
+      <c r="S1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="T1" s="19" t="s">
+      <c r="T1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="U1" s="19" t="s">
+      <c r="U1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="V1" s="19" t="s">
+      <c r="V1" s="1" t="s">
         <v>89</v>
       </c>
     </row>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25christentum/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7725BDF1-1E78-344B-82A7-DA359F159DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B23FEDD-9DD0-7A44-A576-1088E4014A0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="500" windowWidth="33720" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -241,7 +241,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="92">
   <si>
     <t>blank</t>
   </si>
@@ -373,18 +373,12 @@
     <t>Was wird mit wem gefeiert?</t>
   </si>
   <si>
-    <t>Bauer vs. Stark; Ephrem</t>
-  </si>
-  <si>
     <t>Sowohl die innere Logik der orthodoxischen Erzählung als auch historisch-kritische Bemerkungen daran erklären können.</t>
   </si>
   <si>
     <t>Hybridität und Selbstpositionierung zwischen jüdischen Gemeinden und Jesu Nachfolger anhand von Ritualen illustrieren können.</t>
   </si>
   <si>
-    <t>Debattieren: Ob die politische Macht entscheidend war in der Durchsetzung der "Orthodoxie".</t>
-  </si>
-  <si>
     <t>Peter Brown (Interview?)</t>
   </si>
   <si>
@@ -515,6 +509,15 @@
   </si>
   <si>
     <t>slide-filename</t>
+  </si>
+  <si>
+    <t>bauerEinleitungKapitelEdessa1964</t>
+  </si>
+  <si>
+    <t>Eine positive und eine kritische Bemerkung zu Bauers These für sich notieren und bereit sein, diese im Plenum zu diskutieren.</t>
+  </si>
+  <si>
+    <t>bethlehem-church-nativity.jpg</t>
   </si>
 </sst>
 </file>
@@ -1016,7 +1019,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>14</v>
@@ -1052,19 +1055,19 @@
         <v>12</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1082,7 +1085,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>19</v>
@@ -1097,7 +1100,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L2" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B2 &amp; ". " &amp; F2,".",""),"&amp;","")," ","-"),"--","-")</f>
@@ -1254,14 +1257,14 @@
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L3" t="str">
         <f t="shared" ref="L3:L14" si="5">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B3 &amp; ". " &amp; F3,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>2-Heilige-Schriften-und-die-apostolische-Tradition</v>
       </c>
       <c r="M3" s="18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="N3" t="s">
         <v>40</v>
@@ -1395,7 +1398,7 @@
         <v>31</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
         <v>42</v>
@@ -1412,20 +1415,20 @@
         <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L4" t="str">
         <f t="shared" si="5"/>
         <v>3-Abendmahl,-Pessach-und-Ostern</v>
       </c>
       <c r="M4" s="16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="N4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="P4" t="str">
         <f t="shared" si="2"/>
@@ -1542,18 +1545,21 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
+      <c r="K5" t="s">
+        <v>91</v>
+      </c>
       <c r="L5" t="str">
         <f t="shared" si="5"/>
         <v>4-Orthodoxie-und-Häresie</v>
       </c>
       <c r="M5" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="N5" t="s">
         <v>43</v>
       </c>
-      <c r="N5" t="s">
-        <v>44</v>
-      </c>
       <c r="O5" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="P5" t="str">
         <f t="shared" si="2"/>
@@ -1581,8 +1587,8 @@
 session: 4
 tags: [4,slides]
 category: slides
-image: 
-parallaxBackgroundImage: 'assets/img/'
+image: bethlehem-church-nativity.jpg
+parallaxBackgroundImage: 'assets/img/bethlehem-church-nativity.jpg'
 ---
 </v>
       </c>
@@ -1618,8 +1624,8 @@
 session: 4
 tags: [4,slides]
 category: slides
-image: 
-parallaxBackgroundImage: 'assets/img/'
+image: bethlehem-church-nativity.jpg
+parallaxBackgroundImage: 'assets/img/bethlehem-church-nativity.jpg'
 ---
 # Einführung ins Christentum
 {: .r-fit-text}
@@ -1671,20 +1677,20 @@
         <v>5</v>
       </c>
       <c r="K6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L6" t="str">
         <f t="shared" si="5"/>
         <v>5-Askese,-Martyrium,-Wunder-und-Wallfahrt</v>
       </c>
       <c r="M6" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="N6" t="s">
+        <v>46</v>
+      </c>
+      <c r="O6" t="s">
         <v>47</v>
-      </c>
-      <c r="N6" t="s">
-        <v>48</v>
-      </c>
-      <c r="O6" t="s">
-        <v>49</v>
       </c>
       <c r="P6" t="str">
         <f t="shared" si="2"/>
@@ -1788,7 +1794,7 @@
         <v>21</v>
       </c>
       <c r="G7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="4"/>
@@ -1803,10 +1809,10 @@
         <v>6-Exkursion</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="N7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="P7" t="str">
         <f t="shared" si="2"/>
@@ -1995,10 +2001,10 @@
         <v>32</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I9" t="str">
         <f t="shared" si="4"/>
@@ -2009,7 +2015,7 @@
         <v>7</v>
       </c>
       <c r="K9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L9" t="str">
         <f t="shared" si="5"/>
@@ -2019,10 +2025,10 @@
         <v>33</v>
       </c>
       <c r="N9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="O9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="P9" t="str">
         <f t="shared" si="2"/>
@@ -2121,10 +2127,10 @@
         <v>32</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I10" t="str">
         <f t="shared" si="4"/>
@@ -2139,13 +2145,13 @@
         <v>8-Kirche-des-Ostens-(ostsyrisch/assyrianisch)</v>
       </c>
       <c r="M10" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="N10" t="s">
+        <v>54</v>
+      </c>
+      <c r="O10" t="s">
         <v>55</v>
-      </c>
-      <c r="N10" t="s">
-        <v>56</v>
-      </c>
-      <c r="O10" t="s">
-        <v>57</v>
       </c>
       <c r="P10" t="str">
         <f t="shared" si="2"/>
@@ -2246,10 +2252,10 @@
         <v>32</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I11" t="str">
         <f t="shared" si="4"/>
@@ -2264,13 +2270,13 @@
         <v>9-Kopten-und-Syrisch-Orthodoxen</v>
       </c>
       <c r="M11" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N11" t="s">
+        <v>57</v>
+      </c>
+      <c r="O11" t="s">
         <v>58</v>
-      </c>
-      <c r="N11" t="s">
-        <v>59</v>
-      </c>
-      <c r="O11" t="s">
-        <v>60</v>
       </c>
       <c r="P11" t="str">
         <f t="shared" si="2"/>
@@ -2459,10 +2465,10 @@
         <v>32</v>
       </c>
       <c r="F13" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" t="s">
         <v>71</v>
-      </c>
-      <c r="G13" t="s">
-        <v>73</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="4"/>
@@ -2473,20 +2479,20 @@
         <v>10</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L13" t="str">
         <f t="shared" si="5"/>
         <v>10-Armenier-und-Äthiopier</v>
       </c>
       <c r="M13" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N13" t="s">
+        <v>60</v>
+      </c>
+      <c r="O13" t="s">
         <v>61</v>
-      </c>
-      <c r="N13" t="s">
-        <v>62</v>
-      </c>
-      <c r="O13" t="s">
-        <v>63</v>
       </c>
       <c r="P13" t="str">
         <f t="shared" si="2"/>
@@ -2604,10 +2610,10 @@
       </c>
       <c r="M14" s="9"/>
       <c r="N14" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="O14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="P14" t="str">
         <f t="shared" si="2"/>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10511"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25christentum/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B23FEDD-9DD0-7A44-A576-1088E4014A0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE8F203B-276B-704D-892F-FAF5BD333341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="500" windowWidth="33720" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -379,15 +379,9 @@
     <t>Hybridität und Selbstpositionierung zwischen jüdischen Gemeinden und Jesu Nachfolger anhand von Ritualen illustrieren können.</t>
   </si>
   <si>
-    <t>Peter Brown (Interview?)</t>
-  </si>
-  <si>
     <t>Den Heiligkeitsbegriff mit Beispielen erklären können.</t>
   </si>
   <si>
-    <t>Heiligkeitsfaktoren sammeln</t>
-  </si>
-  <si>
     <t>Wie sieht eine Kirche aus?</t>
   </si>
   <si>
@@ -518,6 +512,12 @@
   </si>
   <si>
     <t>bethlehem-church-nativity.jpg</t>
+  </si>
+  <si>
+    <t>georgetownuniversity-theologyCostanLecture20142015</t>
+  </si>
+  <si>
+    <t>Beispiele von heiligen Personen und ihre Heiligkeitsfaktoren hier sammeln: &lt;https://etherpad.studiumdigitale.uni-frankfurt.de/p/25christentum5&gt;. (Als Zusatz zum Video könnten auch Beiträge in Enzyklopädien zu einzelnen Heiligen geschaut werden.)</t>
   </si>
 </sst>
 </file>
@@ -1019,7 +1019,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>14</v>
@@ -1055,19 +1055,19 @@
         <v>12</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="S1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1085,7 +1085,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>19</v>
@@ -1100,7 +1100,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L2" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B2 &amp; ". " &amp; F2,".",""),"&amp;","")," ","-"),"--","-")</f>
@@ -1257,14 +1257,14 @@
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L3" t="str">
         <f t="shared" ref="L3:L14" si="5">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B3 &amp; ". " &amp; F3,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>2-Heilige-Schriften-und-die-apostolische-Tradition</v>
       </c>
       <c r="M3" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="N3" t="s">
         <v>40</v>
@@ -1398,7 +1398,7 @@
         <v>31</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G4" t="s">
         <v>42</v>
@@ -1415,20 +1415,20 @@
         <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L4" t="str">
         <f t="shared" si="5"/>
         <v>3-Abendmahl,-Pessach-und-Ostern</v>
       </c>
       <c r="M4" s="16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="N4" t="s">
         <v>44</v>
       </c>
       <c r="O4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="P4" t="str">
         <f t="shared" si="2"/>
@@ -1546,20 +1546,20 @@
         <v>4</v>
       </c>
       <c r="K5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L5" t="str">
         <f t="shared" si="5"/>
         <v>4-Orthodoxie-und-Häresie</v>
       </c>
       <c r="M5" s="16" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="N5" t="s">
         <v>43</v>
       </c>
       <c r="O5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P5" t="str">
         <f t="shared" si="2"/>
@@ -1677,20 +1677,20 @@
         <v>5</v>
       </c>
       <c r="K6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L6" t="str">
         <f t="shared" si="5"/>
         <v>5-Askese,-Martyrium,-Wunder-und-Wallfahrt</v>
       </c>
       <c r="M6" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="N6" t="s">
         <v>45</v>
       </c>
-      <c r="N6" t="s">
-        <v>46</v>
-      </c>
       <c r="O6" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="P6" t="str">
         <f t="shared" si="2"/>
@@ -1794,7 +1794,7 @@
         <v>21</v>
       </c>
       <c r="G7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="4"/>
@@ -1809,10 +1809,10 @@
         <v>6-Exkursion</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="P7" t="str">
         <f t="shared" si="2"/>
@@ -2001,10 +2001,10 @@
         <v>32</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I9" t="str">
         <f t="shared" si="4"/>
@@ -2015,7 +2015,7 @@
         <v>7</v>
       </c>
       <c r="K9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L9" t="str">
         <f t="shared" si="5"/>
@@ -2025,10 +2025,10 @@
         <v>33</v>
       </c>
       <c r="N9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="O9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="P9" t="str">
         <f t="shared" si="2"/>
@@ -2127,10 +2127,10 @@
         <v>32</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I10" t="str">
         <f t="shared" si="4"/>
@@ -2145,13 +2145,13 @@
         <v>8-Kirche-des-Ostens-(ostsyrisch/assyrianisch)</v>
       </c>
       <c r="M10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" t="s">
+        <v>52</v>
+      </c>
+      <c r="O10" t="s">
         <v>53</v>
-      </c>
-      <c r="N10" t="s">
-        <v>54</v>
-      </c>
-      <c r="O10" t="s">
-        <v>55</v>
       </c>
       <c r="P10" t="str">
         <f t="shared" si="2"/>
@@ -2252,10 +2252,10 @@
         <v>32</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I11" t="str">
         <f t="shared" si="4"/>
@@ -2270,13 +2270,13 @@
         <v>9-Kopten-und-Syrisch-Orthodoxen</v>
       </c>
       <c r="M11" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N11" t="s">
+        <v>55</v>
+      </c>
+      <c r="O11" t="s">
         <v>56</v>
-      </c>
-      <c r="N11" t="s">
-        <v>57</v>
-      </c>
-      <c r="O11" t="s">
-        <v>58</v>
       </c>
       <c r="P11" t="str">
         <f t="shared" si="2"/>
@@ -2465,10 +2465,10 @@
         <v>32</v>
       </c>
       <c r="F13" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" t="s">
         <v>69</v>
-      </c>
-      <c r="G13" t="s">
-        <v>71</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="4"/>
@@ -2479,20 +2479,20 @@
         <v>10</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L13" t="str">
         <f t="shared" si="5"/>
         <v>10-Armenier-und-Äthiopier</v>
       </c>
       <c r="M13" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N13" t="s">
+        <v>58</v>
+      </c>
+      <c r="O13" t="s">
         <v>59</v>
-      </c>
-      <c r="N13" t="s">
-        <v>60</v>
-      </c>
-      <c r="O13" t="s">
-        <v>61</v>
       </c>
       <c r="P13" t="str">
         <f t="shared" si="2"/>
@@ -2610,10 +2610,10 @@
       </c>
       <c r="M14" s="9"/>
       <c r="N14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="O14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="P14" t="str">
         <f t="shared" si="2"/>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25christentum/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE8F203B-276B-704D-892F-FAF5BD333341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46BB309-CA4C-4F44-A12E-0AB257F1170B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -137,6 +137,39 @@
         </r>
       </text>
     </comment>
+    <comment ref="K7" authorId="0" shapeId="0" xr:uid="{AFE426D4-7B1A-9D4C-B10D-18C15CE64E4B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Microsoft Office User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Arabic Bible</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="K9" authorId="0" shapeId="0" xr:uid="{23CF44F8-86FA-7B45-A00A-CC7096BB709D}">
       <text>
         <r>
@@ -241,7 +274,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="91">
   <si>
     <t>blank</t>
   </si>
@@ -340,9 +373,6 @@
   </si>
   <si>
     <t>Die Entfaltung der Gemeinden</t>
-  </si>
-  <si>
-    <t>griffith</t>
   </si>
   <si>
     <t>Schlusswort</t>
@@ -385,9 +415,6 @@
     <t>Wie sieht eine Kirche aus?</t>
   </si>
   <si>
-    <t>something about liturgy?</t>
-  </si>
-  <si>
     <t>Erfahren, wie in einer nicht-westlichen Tradition einen Gottesdienst gefeiert wird.</t>
   </si>
   <si>
@@ -518,6 +545,9 @@
   </si>
   <si>
     <t>Beispiele von heiligen Personen und ihre Heiligkeitsfaktoren hier sammeln: &lt;https://etherpad.studiumdigitale.uni-frankfurt.de/p/25christentum5&gt;. (Als Zusatz zum Video könnten auch Beiträge in Enzyklopädien zu einzelnen Heiligen geschaut werden.)</t>
+  </si>
+  <si>
+    <t>tamckeIslamUndChristentum2008</t>
   </si>
 </sst>
 </file>
@@ -1019,7 +1049,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>14</v>
@@ -1046,7 +1076,7 @@
         <v>10</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>11</v>
@@ -1055,19 +1085,19 @@
         <v>12</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="S1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1085,7 +1115,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>19</v>
@@ -1100,14 +1130,14 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L2" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B2 &amp; ". " &amp; F2,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>1-Einführung-Zielsetzung</v>
       </c>
       <c r="N2" s="17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P2" t="str">
         <f t="shared" ref="P2:P14" si="2">"["&amp;B2&amp;"]"</f>
@@ -1243,7 +1273,7 @@
         <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H3" t="s">
         <v>22</v>
@@ -1257,20 +1287,20 @@
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L3" t="str">
         <f t="shared" ref="L3:L14" si="5">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B3 &amp; ". " &amp; F3,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>2-Heilige-Schriften-und-die-apostolische-Tradition</v>
       </c>
       <c r="M3" s="18" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O3" t="s">
         <v>40</v>
-      </c>
-      <c r="O3" t="s">
-        <v>41</v>
       </c>
       <c r="P3" t="str">
         <f t="shared" si="2"/>
@@ -1398,10 +1428,10 @@
         <v>31</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H4" t="s">
         <v>28</v>
@@ -1415,20 +1445,20 @@
         <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L4" t="str">
         <f t="shared" si="5"/>
         <v>3-Abendmahl,-Pessach-und-Ostern</v>
       </c>
       <c r="M4" s="16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P4" t="str">
         <f t="shared" si="2"/>
@@ -1546,20 +1576,20 @@
         <v>4</v>
       </c>
       <c r="K5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L5" t="str">
         <f t="shared" si="5"/>
         <v>4-Orthodoxie-und-Häresie</v>
       </c>
       <c r="M5" s="16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="N5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="P5" t="str">
         <f t="shared" si="2"/>
@@ -1677,20 +1707,20 @@
         <v>5</v>
       </c>
       <c r="K6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L6" t="str">
         <f t="shared" si="5"/>
         <v>5-Askese,-Martyrium,-Wunder-und-Wallfahrt</v>
       </c>
       <c r="M6" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P6" t="str">
         <f t="shared" si="2"/>
@@ -1744,7 +1774,7 @@
 ## Lektüre
 ## Diskussion
 ## Vorschau
-Wie sieht eine Kirche aus?</v>
+Wie verstanden sich Christen und Muslime?</v>
       </c>
       <c r="V6" t="str">
         <f t="shared" si="10"/>
@@ -1773,7 +1803,7 @@
 ## Lektüre
 ## Diskussion
 ## Vorschau
-Wie sieht eine Kirche aus?</v>
+Wie verstanden sich Christen und Muslime?</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1788,30 +1818,36 @@
         <v>2025-06-02-6.md</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="G7" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="4"/>
-        <v>6. Exkursion: Wie sieht eine Kirche aus?</v>
+        <v>6. Begegnungen mit dem Islam: Wie verstanden sich Christen und Muslime?</v>
       </c>
       <c r="J7" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
+      <c r="K7" t="s">
+        <v>73</v>
+      </c>
       <c r="L7" t="str">
         <f t="shared" si="5"/>
-        <v>6-Exkursion</v>
-      </c>
-      <c r="M7" s="16" t="s">
+        <v>6-Begegnungen-mit-dem-Islam</v>
+      </c>
+      <c r="M7" t="s">
+        <v>90</v>
+      </c>
+      <c r="N7" t="s">
         <v>47</v>
       </c>
-      <c r="N7" t="s">
+      <c r="O7" t="s">
         <v>48</v>
       </c>
       <c r="P7" t="str">
@@ -1835,13 +1871,13 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">---
 layout: reveal
-title: 'Wie sieht eine Kirche aus?'
+title: 'Wie verstanden sich Christen und Muslime?'
 author: 'Nathan Gibson'
 session: 6
 tags: [6,slides]
 category: slides
-image: 
-parallaxBackgroundImage: 'assets/img/'
+image: st-paul-harissa.jpg
+parallaxBackgroundImage: 'assets/img/st-paul-harissa.jpg'
 ---
 </v>
       </c>
@@ -1849,7 +1885,7 @@
         <f t="shared" si="8"/>
         <v># Einführung ins Christentum
 {: .r-fit-text}
-### Wie sieht eine Kirche aus?
+### Wie verstanden sich Christen und Muslime?
 Sommersemester 2025
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
@@ -1858,7 +1894,7 @@
 ## Projekt
 ## Einleitung
 ## Heutiges Lernziel
-Erfahren, wie in einer nicht-westlichen Tradition einen Gottesdienst gefeiert wird.</v>
+Einige Bereiche nennen können, in denen der langjährige Austausch zwischen islamischen und ostkirchlichen Gemeinschaften besonders bedeutsam war.</v>
       </c>
       <c r="U7" t="str">
         <f t="shared" si="9"/>
@@ -1872,17 +1908,17 @@
         <f t="shared" si="10"/>
         <v xml:space="preserve">---
 layout: reveal
-title: 'Wie sieht eine Kirche aus?'
+title: 'Wie verstanden sich Christen und Muslime?'
 author: 'Nathan Gibson'
 session: 6
 tags: [6,slides]
 category: slides
-image: 
-parallaxBackgroundImage: 'assets/img/'
+image: st-paul-harissa.jpg
+parallaxBackgroundImage: 'assets/img/st-paul-harissa.jpg'
 ---
 # Einführung ins Christentum
 {: .r-fit-text}
-### Wie sieht eine Kirche aus?
+### Wie verstanden sich Christen und Muslime?
 Sommersemester 2025
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
@@ -1891,7 +1927,7 @@
 ## Projekt
 ## Einleitung
 ## Heutiges Lernziel
-Erfahren, wie in einer nicht-westlichen Tradition einen Gottesdienst gefeiert wird.
+Einige Bereiche nennen können, in denen der langjährige Austausch zwischen islamischen und ostkirchlichen Gemeinschaften besonders bedeutsam war.
 ## Lektüre
 ## Diskussion
 ## Vorschau
@@ -1942,7 +1978,7 @@
 Sommersemester 2025
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-Erfahren, wie in einer nicht-westlichen Tradition einen Gottesdienst gefeiert wird.
+Einige Bereiche nennen können, in denen der langjährige Austausch zwischen islamischen und ostkirchlichen Gemeinschaften besonders bedeutsam war.
 ## 📈 Rückblick: 
 ## Projekt
 ## Einleitung
@@ -1955,7 +1991,7 @@
 ## Lektüre
 ## Diskussion
 ## Vorschau
-Wie verstanden sich Christen und Muslime?</v>
+Wie sieht eine Kirche aus?</v>
       </c>
       <c r="V8" t="str">
         <f t="shared" si="10"/>
@@ -1975,7 +2011,7 @@
 Sommersemester 2025
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-Erfahren, wie in einer nicht-westlichen Tradition einen Gottesdienst gefeiert wird.
+Einige Bereiche nennen können, in denen der langjährige Austausch zwischen islamischen und ostkirchlichen Gemeinschaften besonders bedeutsam war.
 ## 📈 Rückblick: 
 ## Projekt
 ## Einleitung
@@ -1983,7 +2019,7 @@
 ## Lektüre
 ## Diskussion
 ## Vorschau
-Wie verstanden sich Christen und Muslime?</v>
+Wie sieht eine Kirche aus?</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1998,37 +2034,29 @@
         <v>2025-06-16-7.md</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="G9" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="I9" t="str">
         <f t="shared" si="4"/>
-        <v>7. Begegnungen mit dem Islam: Wie verstanden sich Christen und Muslime?</v>
+        <v>7. Exkursion: Wie sieht eine Kirche aus?</v>
       </c>
       <c r="J9" s="3">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="K9" t="s">
-        <v>75</v>
-      </c>
       <c r="L9" t="str">
         <f t="shared" si="5"/>
-        <v>7-Begegnungen-mit-dem-Islam</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>33</v>
-      </c>
+        <v>7-Exkursion</v>
+      </c>
+      <c r="M9" s="16"/>
       <c r="N9" t="s">
-        <v>49</v>
-      </c>
-      <c r="O9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="P9" t="str">
         <f t="shared" si="2"/>
@@ -2051,13 +2079,13 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">---
 layout: reveal
-title: 'Wie verstanden sich Christen und Muslime?'
+title: 'Wie sieht eine Kirche aus?'
 author: 'Nathan Gibson'
 session: 7
 tags: [7,slides]
 category: slides
-image: st-paul-harissa.jpg
-parallaxBackgroundImage: 'assets/img/st-paul-harissa.jpg'
+image: 
+parallaxBackgroundImage: 'assets/img/'
 ---
 </v>
       </c>
@@ -2065,7 +2093,7 @@
         <f t="shared" si="8"/>
         <v># Einführung ins Christentum
 {: .r-fit-text}
-### Wie verstanden sich Christen und Muslime?
+### Wie sieht eine Kirche aus?
 Sommersemester 2025
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
@@ -2073,7 +2101,7 @@
 ## Projekt
 ## Einleitung
 ## Heutiges Lernziel
-Einige Bereiche nennen können, in denen der langjährige Austausch zwischen islamischen und ostkirchlichen Gemeinschaften besonders bedeutsam war.</v>
+Erfahren, wie in einer nicht-westlichen Tradition einen Gottesdienst gefeiert wird.</v>
       </c>
       <c r="U9" t="str">
         <f t="shared" si="9"/>
@@ -2087,17 +2115,17 @@
         <f t="shared" si="10"/>
         <v>---
 layout: reveal
-title: 'Wie verstanden sich Christen und Muslime?'
+title: 'Wie sieht eine Kirche aus?'
 author: 'Nathan Gibson'
 session: 7
 tags: [7,slides]
 category: slides
-image: st-paul-harissa.jpg
-parallaxBackgroundImage: 'assets/img/st-paul-harissa.jpg'
+image: 
+parallaxBackgroundImage: 'assets/img/'
 ---
 # Einführung ins Christentum
 {: .r-fit-text}
-### Wie verstanden sich Christen und Muslime?
+### Wie sieht eine Kirche aus?
 Sommersemester 2025
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
@@ -2105,7 +2133,7 @@
 ## Projekt
 ## Einleitung
 ## Heutiges Lernziel
-Einige Bereiche nennen können, in denen der langjährige Austausch zwischen islamischen und ostkirchlichen Gemeinschaften besonders bedeutsam war.
+Erfahren, wie in einer nicht-westlichen Tradition einen Gottesdienst gefeiert wird.
 ## Lektüre
 ## Diskussion
 ## Vorschau
@@ -2127,10 +2155,10 @@
         <v>32</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I10" t="str">
         <f t="shared" si="4"/>
@@ -2145,13 +2173,13 @@
         <v>8-Kirche-des-Ostens-(ostsyrisch/assyrianisch)</v>
       </c>
       <c r="M10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N10" t="s">
+        <v>50</v>
+      </c>
+      <c r="O10" t="s">
         <v>51</v>
-      </c>
-      <c r="N10" t="s">
-        <v>52</v>
-      </c>
-      <c r="O10" t="s">
-        <v>53</v>
       </c>
       <c r="P10" t="str">
         <f t="shared" si="2"/>
@@ -2192,7 +2220,7 @@
 Sommersemester 2025
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-Einige Bereiche nennen können, in denen der langjährige Austausch zwischen islamischen und ostkirchlichen Gemeinschaften besonders bedeutsam war.
+Erfahren, wie in einer nicht-westlichen Tradition einen Gottesdienst gefeiert wird.
 ## 📈 Rückblick: 
 ## Projekt
 ## Einleitung
@@ -2225,7 +2253,7 @@
 Sommersemester 2025
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-Einige Bereiche nennen können, in denen der langjährige Austausch zwischen islamischen und ostkirchlichen Gemeinschaften besonders bedeutsam war.
+Erfahren, wie in einer nicht-westlichen Tradition einen Gottesdienst gefeiert wird.
 ## 📈 Rückblick: 
 ## Projekt
 ## Einleitung
@@ -2252,10 +2280,10 @@
         <v>32</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I11" t="str">
         <f t="shared" si="4"/>
@@ -2270,13 +2298,13 @@
         <v>9-Kopten-und-Syrisch-Orthodoxen</v>
       </c>
       <c r="M11" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="N11" t="s">
+        <v>53</v>
+      </c>
+      <c r="O11" t="s">
         <v>54</v>
-      </c>
-      <c r="N11" t="s">
-        <v>55</v>
-      </c>
-      <c r="O11" t="s">
-        <v>56</v>
       </c>
       <c r="P11" t="str">
         <f t="shared" si="2"/>
@@ -2465,10 +2493,10 @@
         <v>32</v>
       </c>
       <c r="F13" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" t="s">
         <v>67</v>
-      </c>
-      <c r="G13" t="s">
-        <v>69</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="4"/>
@@ -2479,20 +2507,20 @@
         <v>10</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L13" t="str">
         <f t="shared" si="5"/>
         <v>10-Armenier-und-Äthiopier</v>
       </c>
       <c r="M13" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N13" t="s">
+        <v>56</v>
+      </c>
+      <c r="O13" t="s">
         <v>57</v>
-      </c>
-      <c r="N13" t="s">
-        <v>58</v>
-      </c>
-      <c r="O13" t="s">
-        <v>59</v>
       </c>
       <c r="P13" t="str">
         <f t="shared" si="2"/>
@@ -2588,13 +2616,13 @@
         <v>2025-07-21-11.md</v>
       </c>
       <c r="E14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="G14" t="s">
         <v>35</v>
-      </c>
-      <c r="G14" t="s">
-        <v>36</v>
       </c>
       <c r="I14" t="str">
         <f t="shared" si="4"/>
@@ -2610,10 +2638,10 @@
       </c>
       <c r="M14" s="9"/>
       <c r="N14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="O14" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="P14" t="str">
         <f t="shared" si="2"/>
@@ -2704,6 +2732,7 @@
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25christentum/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46BB309-CA4C-4F44-A12E-0AB257F1170B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD17818-17A8-874E-AB68-09D6778A925F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -274,7 +274,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="95">
   <si>
     <t>blank</t>
   </si>
@@ -548,6 +548,18 @@
   </si>
   <si>
     <t>tamckeIslamUndChristentum2008</t>
+  </si>
+  <si>
+    <t>coptic-incense.jpg</t>
+  </si>
+  <si>
+    <t>coptic-michael.jpg</t>
+  </si>
+  <si>
+    <t>bl-add-ms-7170-resurrection.jpg</t>
+  </si>
+  <si>
+    <t>wadi-qelt.jpg</t>
   </si>
 </sst>
 </file>
@@ -1991,7 +2003,7 @@
 ## Lektüre
 ## Diskussion
 ## Vorschau
-Wie sieht eine Kirche aus?</v>
+Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (I)</v>
       </c>
       <c r="V8" t="str">
         <f t="shared" si="10"/>
@@ -2019,7 +2031,7 @@
 ## Lektüre
 ## Diskussion
 ## Vorschau
-Wie sieht eine Kirche aus?</v>
+Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (I)</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2034,29 +2046,37 @@
         <v>2025-06-16-7.md</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="G9" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="I9" t="str">
         <f t="shared" si="4"/>
-        <v>7. Exkursion: Wie sieht eine Kirche aus?</v>
+        <v>7. Kirche des Ostens (ostsyrisch/assyrianisch): Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (I)</v>
       </c>
       <c r="J9" s="3">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
+      <c r="K9" t="s">
+        <v>93</v>
+      </c>
       <c r="L9" t="str">
         <f t="shared" si="5"/>
-        <v>7-Exkursion</v>
-      </c>
-      <c r="M9" s="16"/>
+        <v>7-Kirche-des-Ostens-(ostsyrisch/assyrianisch)</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N9" t="s">
-        <v>46</v>
+        <v>50</v>
+      </c>
+      <c r="O9" t="s">
+        <v>51</v>
       </c>
       <c r="P9" t="str">
         <f t="shared" si="2"/>
@@ -2076,16 +2096,26 @@
         <v>2025-06-16-7-slides.md</v>
       </c>
       <c r="S9" t="str">
-        <f t="shared" si="7"/>
+        <f>"---
+layout: reveal
+title: '"&amp;G9&amp;"'
+author: 'Nathan Gibson'
+session: "&amp;B9&amp;"
+tags: ["&amp;B9&amp;",slides]
+category: slides
+image: "&amp;K9&amp;"
+parallaxBackgroundImage: 'assets/img/"&amp;K9&amp;"'
+---
+"</f>
         <v xml:space="preserve">---
 layout: reveal
-title: 'Wie sieht eine Kirche aus?'
+title: 'Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (I)'
 author: 'Nathan Gibson'
 session: 7
 tags: [7,slides]
 category: slides
-image: 
-parallaxBackgroundImage: 'assets/img/'
+image: bl-add-ms-7170-resurrection.jpg
+parallaxBackgroundImage: 'assets/img/bl-add-ms-7170-resurrection.jpg'
 ---
 </v>
       </c>
@@ -2093,7 +2123,7 @@
         <f t="shared" si="8"/>
         <v># Einführung ins Christentum
 {: .r-fit-text}
-### Wie sieht eine Kirche aus?
+### Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (I)
 Sommersemester 2025
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
@@ -2101,7 +2131,7 @@
 ## Projekt
 ## Einleitung
 ## Heutiges Lernziel
-Erfahren, wie in einer nicht-westlichen Tradition einen Gottesdienst gefeiert wird.</v>
+Die größten Gemeinsamkeiten und Unterschiede zwischen der Kirche des Ostens und den griechischen oder römischen Kirchen identifizieren.</v>
       </c>
       <c r="U9" t="str">
         <f t="shared" si="9"/>
@@ -2109,143 +2139,19 @@
 ## Lektüre
 ## Diskussion
 ## Vorschau
-Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (I)</v>
+Wie entfalteten sich die einheimischen Kirchen innerhalb des Römischen Reiches? </v>
       </c>
       <c r="V9" t="str">
         <f t="shared" si="10"/>
-        <v>---
-layout: reveal
-title: 'Wie sieht eine Kirche aus?'
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (I)'
 author: 'Nathan Gibson'
 session: 7
 tags: [7,slides]
 category: slides
-image: 
-parallaxBackgroundImage: 'assets/img/'
----
-# Einführung ins Christentum
-{: .r-fit-text}
-### Wie sieht eine Kirche aus?
-Sommersemester 2025
-Prof. Dr. Nathan Gibson
-## 📈 Rückblick: Lernziel
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
-Erfahren, wie in einer nicht-westlichen Tradition einen Gottesdienst gefeiert wird.
-## Lektüre
-## Diskussion
-## Vorschau
-Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (I)</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="3">
-        <v>8</v>
-      </c>
-      <c r="C10" s="8">
-        <v>45831</v>
-      </c>
-      <c r="D10" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>2025-06-23-8.md</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G10" t="s">
-        <v>66</v>
-      </c>
-      <c r="I10" t="str">
-        <f t="shared" si="4"/>
-        <v>8. Kirche des Ostens (ostsyrisch/assyrianisch): Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (I)</v>
-      </c>
-      <c r="J10" s="3">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="L10" t="str">
-        <f t="shared" si="5"/>
-        <v>8-Kirche-des-Ostens-(ostsyrisch/assyrianisch)</v>
-      </c>
-      <c r="M10" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="N10" t="s">
-        <v>50</v>
-      </c>
-      <c r="O10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P10" t="str">
-        <f t="shared" si="2"/>
-        <v>[8]</v>
-      </c>
-      <c r="Q10" t="str">
-        <f t="shared" si="3"/>
-        <v>---
-layout: post
-session: 8
-tags: [8]
-level: overview
----</v>
-      </c>
-      <c r="R10" t="str">
-        <f t="shared" si="6"/>
-        <v>2025-06-23-8-slides.md</v>
-      </c>
-      <c r="S10" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">---
-layout: reveal
-title: 'Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (I)'
-author: 'Nathan Gibson'
-session: 8
-tags: [8,slides]
-category: slides
-image: 
-parallaxBackgroundImage: 'assets/img/'
----
-</v>
-      </c>
-      <c r="T10" t="str">
-        <f t="shared" si="8"/>
-        <v># Einführung ins Christentum
-{: .r-fit-text}
-### Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (I)
-Sommersemester 2025
-Prof. Dr. Nathan Gibson
-## 📈 Rückblick: Lernziel
-Erfahren, wie in einer nicht-westlichen Tradition einen Gottesdienst gefeiert wird.
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
-Die größten Gemeinsamkeiten und Unterschiede zwischen der Kirche des Ostens und den griechischen oder römischen Kirchen identifizieren.</v>
-      </c>
-      <c r="U10" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">
-## Lektüre
-## Diskussion
-## Vorschau
-Wie entfalteten sich die einheimischen Kirchen innerhalb des Römischen Reiches? </v>
-      </c>
-      <c r="V10" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">---
-layout: reveal
-title: 'Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (I)'
-author: 'Nathan Gibson'
-session: 8
-tags: [8,slides]
-category: slides
-image: 
-parallaxBackgroundImage: 'assets/img/'
+image: bl-add-ms-7170-resurrection.jpg
+parallaxBackgroundImage: 'assets/img/bl-add-ms-7170-resurrection.jpg'
 ---
 # Einführung ins Christentum
 {: .r-fit-text}
@@ -2253,7 +2159,6 @@
 Sommersemester 2025
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-Erfahren, wie in einer nicht-westlichen Tradition einen Gottesdienst gefeiert wird.
 ## 📈 Rückblick: 
 ## Projekt
 ## Einleitung
@@ -2265,79 +2170,92 @@
 Wie entfalteten sich die einheimischen Kirchen innerhalb des Römischen Reiches? </v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="3">
-        <v>9</v>
-      </c>
-      <c r="C11" s="8">
-        <v>45838</v>
-      </c>
-      <c r="D11" s="4" t="str">
+    <row r="10" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="3">
+        <v>8</v>
+      </c>
+      <c r="C10" s="8">
+        <v>45831</v>
+      </c>
+      <c r="D10" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>2025-06-30-9.md</v>
-      </c>
-      <c r="E11" s="4" t="s">
+        <v>2025-06-23-8.md</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G10" t="s">
         <v>68</v>
       </c>
-      <c r="I11" t="str">
+      <c r="I10" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">9. Kopten und Syrisch-Orthodoxen: Wie entfalteten sich die einheimischen Kirchen innerhalb des Römischen Reiches? </v>
-      </c>
-      <c r="J11" s="3">
+        <v xml:space="preserve">8. Kopten und Syrisch-Orthodoxen: Wie entfalteten sich die einheimischen Kirchen innerhalb des Römischen Reiches? </v>
+      </c>
+      <c r="J10" s="3">
         <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="L11" t="str">
+        <v>8</v>
+      </c>
+      <c r="K10" t="s">
+        <v>92</v>
+      </c>
+      <c r="L10" t="str">
         <f t="shared" si="5"/>
-        <v>9-Kopten-und-Syrisch-Orthodoxen</v>
-      </c>
-      <c r="M11" s="16" t="s">
+        <v>8-Kopten-und-Syrisch-Orthodoxen</v>
+      </c>
+      <c r="M10" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="N11" t="s">
+      <c r="N10" t="s">
         <v>53</v>
       </c>
-      <c r="O11" t="s">
+      <c r="O10" t="s">
         <v>54</v>
       </c>
-      <c r="P11" t="str">
+      <c r="P10" t="str">
         <f t="shared" si="2"/>
-        <v>[9]</v>
-      </c>
-      <c r="Q11" t="str">
+        <v>[8]</v>
+      </c>
+      <c r="Q10" t="str">
         <f t="shared" si="3"/>
         <v>---
 layout: post
-session: 9
-tags: [9]
+session: 8
+tags: [8]
 level: overview
 ---</v>
       </c>
-      <c r="R11" t="str">
+      <c r="R10" t="str">
         <f t="shared" si="6"/>
-        <v>2025-06-30-9-slides.md</v>
-      </c>
-      <c r="S11" t="str">
-        <f t="shared" si="7"/>
+        <v>2025-06-23-8-slides.md</v>
+      </c>
+      <c r="S10" t="str">
+        <f>"---
+layout: reveal
+title: '"&amp;G10&amp;"'
+author: 'Nathan Gibson'
+session: "&amp;B10&amp;"
+tags: ["&amp;B10&amp;",slides]
+category: slides
+image: "&amp;K10&amp;"
+parallaxBackgroundImage: 'assets/img/"&amp;K10&amp;"'
+---
+"</f>
         <v xml:space="preserve">---
 layout: reveal
 title: 'Wie entfalteten sich die einheimischen Kirchen innerhalb des Römischen Reiches? '
 author: 'Nathan Gibson'
-session: 9
-tags: [9,slides]
-category: slides
-image: 
-parallaxBackgroundImage: 'assets/img/'
+session: 8
+tags: [8,slides]
+category: slides
+image: coptic-michael.jpg
+parallaxBackgroundImage: 'assets/img/coptic-michael.jpg'
 ---
 </v>
       </c>
-      <c r="T11" t="str">
+      <c r="T10" t="str">
         <f t="shared" si="8"/>
         <v># Einführung ins Christentum
 {: .r-fit-text}
@@ -2352,25 +2270,25 @@
 ## Heutiges Lernziel
 Einige Aspekte der Identitätserzählung der koptischen und syrisch-orthodoxischen Gemeinden zusammenfassen können.</v>
       </c>
-      <c r="U11" t="str">
+      <c r="U10" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve">
 ## Lektüre
 ## Diskussion
 ## Vorschau
-</v>
-      </c>
-      <c r="V11" t="str">
+Wie sieht eine Kirche aus?</v>
+      </c>
+      <c r="V10" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve">---
+        <v>---
 layout: reveal
 title: 'Wie entfalteten sich die einheimischen Kirchen innerhalb des Römischen Reiches? '
 author: 'Nathan Gibson'
-session: 9
-tags: [9,slides]
-category: slides
-image: 
-parallaxBackgroundImage: 'assets/img/'
+session: 8
+tags: [8,slides]
+category: slides
+image: coptic-michael.jpg
+parallaxBackgroundImage: 'assets/img/coptic-michael.jpg'
 ---
 # Einführung ins Christentum
 {: .r-fit-text}
@@ -2387,6 +2305,129 @@
 ## Lektüre
 ## Diskussion
 ## Vorschau
+Wie sieht eine Kirche aus?</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="3">
+        <v>9</v>
+      </c>
+      <c r="C11" s="8">
+        <v>45838</v>
+      </c>
+      <c r="D11" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>2025-06-30-9.md</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="4"/>
+        <v>9. Exkursion: Wie sieht eine Kirche aus?</v>
+      </c>
+      <c r="J11" s="3">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="K11" t="s">
+        <v>91</v>
+      </c>
+      <c r="L11" t="str">
+        <f t="shared" si="5"/>
+        <v>9-Exkursion</v>
+      </c>
+      <c r="M11" s="16"/>
+      <c r="N11" t="s">
+        <v>46</v>
+      </c>
+      <c r="P11" t="str">
+        <f t="shared" si="2"/>
+        <v>[9]</v>
+      </c>
+      <c r="Q11" t="str">
+        <f t="shared" si="3"/>
+        <v>---
+layout: post
+session: 9
+tags: [9]
+level: overview
+---</v>
+      </c>
+      <c r="R11" t="str">
+        <f t="shared" si="6"/>
+        <v>2025-06-30-9-slides.md</v>
+      </c>
+      <c r="S11" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Wie sieht eine Kirche aus?'
+author: 'Nathan Gibson'
+session: 9
+tags: [9,slides]
+category: slides
+image: coptic-incense.jpg
+parallaxBackgroundImage: 'assets/img/coptic-incense.jpg'
+---
+</v>
+      </c>
+      <c r="T11" t="str">
+        <f t="shared" si="8"/>
+        <v># Einführung ins Christentum
+{: .r-fit-text}
+### Wie sieht eine Kirche aus?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Einige Aspekte der Identitätserzählung der koptischen und syrisch-orthodoxischen Gemeinden zusammenfassen können.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Erfahren, wie in einer nicht-westlichen Tradition einen Gottesdienst gefeiert wird.</v>
+      </c>
+      <c r="U11" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+</v>
+      </c>
+      <c r="V11" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Wie sieht eine Kirche aus?'
+author: 'Nathan Gibson'
+session: 9
+tags: [9,slides]
+category: slides
+image: coptic-incense.jpg
+parallaxBackgroundImage: 'assets/img/coptic-incense.jpg'
+---
+# Einführung ins Christentum
+{: .r-fit-text}
+### Wie sieht eine Kirche aus?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Einige Aspekte der Identitätserzählung der koptischen und syrisch-orthodoxischen Gemeinden zusammenfassen können.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Erfahren, wie in einer nicht-westlichen Tradition einen Gottesdienst gefeiert wird.
+## Lektüre
+## Diskussion
+## Vorschau
 </v>
       </c>
     </row>
@@ -2434,7 +2475,7 @@
 Sommersemester 2025
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-Einige Aspekte der Identitätserzählung der koptischen und syrisch-orthodoxischen Gemeinden zusammenfassen können.
+Erfahren, wie in einer nicht-westlichen Tradition einen Gottesdienst gefeiert wird.
 ## 📈 Rückblick: 
 ## Projekt
 ## Einleitung
@@ -2467,7 +2508,7 @@
 Sommersemester 2025
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-Einige Aspekte der Identitätserzählung der koptischen und syrisch-orthodoxischen Gemeinden zusammenfassen können.
+Erfahren, wie in einer nicht-westlichen Tradition einen Gottesdienst gefeiert wird.
 ## 📈 Rückblick: 
 ## Projekt
 ## Einleitung
@@ -2632,6 +2673,9 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
+      <c r="K14" t="s">
+        <v>94</v>
+      </c>
       <c r="L14" t="str">
         <f t="shared" si="5"/>
         <v>11-Rückblick</v>
@@ -2669,8 +2713,8 @@
 session: 11
 tags: [11,slides]
 category: slides
-image: 
-parallaxBackgroundImage: 'assets/img/'
+image: wadi-qelt.jpg
+parallaxBackgroundImage: 'assets/img/wadi-qelt.jpg'
 ---
 </v>
       </c>
@@ -2706,8 +2750,8 @@
 session: 11
 tags: [11,slides]
 category: slides
-image: 
-parallaxBackgroundImage: 'assets/img/'
+image: wadi-qelt.jpg
+parallaxBackgroundImage: 'assets/img/wadi-qelt.jpg'
 ---
 # Einführung ins Christentum
 {: .r-fit-text}

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25christentum/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD17818-17A8-874E-AB68-09D6778A925F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9C2310-CA71-A740-BAF4-5F47068BEDC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -36,6 +36,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Microsoft Office User</author>
+    <author>tc={3F10DD45-61EC-6140-A23C-727EF741A4D9}</author>
   </authors>
   <commentList>
     <comment ref="K3" authorId="0" shapeId="0" xr:uid="{61B32DDB-B5B9-0142-913E-6250695D5EAF}">
@@ -236,6 +237,14 @@
         </r>
       </text>
     </comment>
+    <comment ref="M10" authorId="1" shapeId="0" xr:uid="{3F10DD45-61EC-6140-A23C-727EF741A4D9}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Volker Menze or Vince Bantu interview/Bantu book</t>
+      </text>
+    </comment>
     <comment ref="K11" authorId="0" shapeId="0" xr:uid="{D73E6C6F-C73A-DC40-90D2-B0CA652CEFEF}">
       <text>
         <r>
@@ -274,7 +283,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="93">
   <si>
     <t>blank</t>
   </si>
@@ -424,27 +433,18 @@
     <t>So viele wie möglich "ersten" unter christlich-arabischen Autoren auflisten: z.B. erster Text, erste Bibelübersetzung, erster Autor den wir namentlich kennen.</t>
   </si>
   <si>
-    <t>Baum-Winkler</t>
-  </si>
-  <si>
     <t>Die größten Gemeinsamkeiten und Unterschiede zwischen der Kirche des Ostens und den griechischen oder römischen Kirchen identifizieren.</t>
   </si>
   <si>
     <t>Orten auf einer Landkarte identifizieren, die mit der Kirche des Ostens verbunden sind.</t>
   </si>
   <si>
-    <t>Volker Menze or Vince Bantu interview/Bantu book</t>
-  </si>
-  <si>
     <t>Einige Aspekte der Identitätserzählung der koptischen und syrisch-orthodoxischen Gemeinden zusammenfassen können.</t>
   </si>
   <si>
     <t>Gemeinsamkeiten und Unterschiede zwischen Kopten und Syrisch-Orthodoxen auflisten.</t>
   </si>
   <si>
-    <t>GCT?</t>
-  </si>
-  <si>
     <t>Eckpunkte der armenischen und äthiopischen Selbstnarrativen erzählen können.</t>
   </si>
   <si>
@@ -560,6 +560,9 @@
   </si>
   <si>
     <t>wadi-qelt.jpg</t>
+  </si>
+  <si>
+    <t>baumZeitalterAraber2000</t>
   </si>
 </sst>
 </file>
@@ -731,6 +734,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Nathan Gibson" id="{0B063AB0-C045-794A-8C2E-DE2C142AB479}" userId="24ad1282b7b2ce07" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1016,6 +1025,14 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="M10" dT="2025-06-02T08:55:10.82" personId="{0B063AB0-C045-794A-8C2E-DE2C142AB479}" id="{3F10DD45-61EC-6140-A23C-727EF741A4D9}">
+    <text>Volker Menze or Vince Bantu interview/Bantu book</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
@@ -1061,7 +1078,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>14</v>
@@ -1097,19 +1114,19 @@
         <v>12</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="S1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1127,7 +1144,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>19</v>
@@ -1142,7 +1159,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L2" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B2 &amp; ". " &amp; F2,".",""),"&amp;","")," ","-"),"--","-")</f>
@@ -1299,14 +1316,14 @@
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L3" t="str">
         <f t="shared" ref="L3:L14" si="5">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B3 &amp; ". " &amp; F3,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>2-Heilige-Schriften-und-die-apostolische-Tradition</v>
       </c>
       <c r="M3" s="18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N3" t="s">
         <v>39</v>
@@ -1440,7 +1457,7 @@
         <v>31</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G4" t="s">
         <v>41</v>
@@ -1457,20 +1474,20 @@
         <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L4" t="str">
         <f t="shared" si="5"/>
         <v>3-Abendmahl,-Pessach-und-Ostern</v>
       </c>
       <c r="M4" s="16" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="N4" t="s">
         <v>43</v>
       </c>
       <c r="O4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P4" t="str">
         <f t="shared" si="2"/>
@@ -1588,20 +1605,20 @@
         <v>4</v>
       </c>
       <c r="K5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L5" t="str">
         <f t="shared" si="5"/>
         <v>4-Orthodoxie-und-Häresie</v>
       </c>
       <c r="M5" s="16" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="N5" t="s">
         <v>42</v>
       </c>
       <c r="O5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="P5" t="str">
         <f t="shared" si="2"/>
@@ -1719,20 +1736,20 @@
         <v>5</v>
       </c>
       <c r="K6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="L6" t="str">
         <f t="shared" si="5"/>
         <v>5-Askese,-Martyrium,-Wunder-und-Wallfahrt</v>
       </c>
       <c r="M6" s="16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N6" t="s">
         <v>44</v>
       </c>
       <c r="O6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P6" t="str">
         <f t="shared" si="2"/>
@@ -1833,10 +1850,10 @@
         <v>32</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="4"/>
@@ -1847,14 +1864,14 @@
         <v>6</v>
       </c>
       <c r="K7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="L7" t="str">
         <f t="shared" si="5"/>
         <v>6-Begegnungen-mit-dem-Islam</v>
       </c>
       <c r="M7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="N7" t="s">
         <v>47</v>
@@ -2049,10 +2066,10 @@
         <v>32</v>
       </c>
       <c r="F9" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G9" t="s">
         <v>63</v>
-      </c>
-      <c r="G9" t="s">
-        <v>66</v>
       </c>
       <c r="I9" t="str">
         <f t="shared" si="4"/>
@@ -2063,20 +2080,20 @@
         <v>7</v>
       </c>
       <c r="K9" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="L9" t="str">
         <f t="shared" si="5"/>
         <v>7-Kirche-des-Ostens-(ostsyrisch/assyrianisch)</v>
       </c>
       <c r="M9" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="N9" t="s">
         <v>49</v>
       </c>
-      <c r="N9" t="s">
+      <c r="O9" t="s">
         <v>50</v>
-      </c>
-      <c r="O9" t="s">
-        <v>51</v>
       </c>
       <c r="P9" t="str">
         <f t="shared" si="2"/>
@@ -2185,10 +2202,10 @@
         <v>32</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G10" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I10" t="str">
         <f t="shared" si="4"/>
@@ -2199,20 +2216,18 @@
         <v>8</v>
       </c>
       <c r="K10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="L10" t="str">
         <f t="shared" si="5"/>
         <v>8-Kopten-und-Syrisch-Orthodoxen</v>
       </c>
-      <c r="M10" s="16" t="s">
+      <c r="M10" s="16"/>
+      <c r="N10" t="s">
+        <v>51</v>
+      </c>
+      <c r="O10" t="s">
         <v>52</v>
-      </c>
-      <c r="N10" t="s">
-        <v>53</v>
-      </c>
-      <c r="O10" t="s">
-        <v>54</v>
       </c>
       <c r="P10" t="str">
         <f t="shared" si="2"/>
@@ -2337,7 +2352,7 @@
         <v>9</v>
       </c>
       <c r="K11" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L11" t="str">
         <f t="shared" si="5"/>
@@ -2534,10 +2549,10 @@
         <v>32</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G13" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="4"/>
@@ -2548,20 +2563,18 @@
         <v>10</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L13" t="str">
         <f t="shared" si="5"/>
         <v>10-Armenier-und-Äthiopier</v>
       </c>
-      <c r="M13" s="16" t="s">
-        <v>55</v>
-      </c>
+      <c r="M13" s="16"/>
       <c r="N13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="O13" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="P13" t="str">
         <f t="shared" si="2"/>
@@ -2674,7 +2687,7 @@
         <v>11</v>
       </c>
       <c r="K14" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L14" t="str">
         <f t="shared" si="5"/>
@@ -2682,10 +2695,10 @@
       </c>
       <c r="M14" s="9"/>
       <c r="N14" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O14" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="P14" t="str">
         <f t="shared" si="2"/>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10608"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25christentum/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9C2310-CA71-A740-BAF4-5F47068BEDC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A78B6D9-8302-4147-82E5-82E6FE8C382B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,6 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Microsoft Office User</author>
-    <author>tc={3F10DD45-61EC-6140-A23C-727EF741A4D9}</author>
   </authors>
   <commentList>
     <comment ref="K3" authorId="0" shapeId="0" xr:uid="{61B32DDB-B5B9-0142-913E-6250695D5EAF}">
@@ -237,14 +236,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="M10" authorId="1" shapeId="0" xr:uid="{3F10DD45-61EC-6140-A23C-727EF741A4D9}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Volker Menze or Vince Bantu interview/Bantu book</t>
-      </text>
-    </comment>
     <comment ref="K11" authorId="0" shapeId="0" xr:uid="{D73E6C6F-C73A-DC40-90D2-B0CA652CEFEF}">
       <text>
         <r>
@@ -283,7 +274,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="94">
   <si>
     <t>blank</t>
   </si>
@@ -563,6 +554,9 @@
   </si>
   <si>
     <t>baumZeitalterAraber2000</t>
+  </si>
+  <si>
+    <t>bantuFirstChristiansAfrica2020</t>
   </si>
 </sst>
 </file>
@@ -574,9 +568,16 @@
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="166" formatCode="dd\.mm"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -677,18 +678,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -698,26 +699,27 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -737,9 +739,7 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Nathan Gibson" id="{0B063AB0-C045-794A-8C2E-DE2C142AB479}" userId="24ad1282b7b2ce07" providerId="Windows Live"/>
-</personList>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1025,14 +1025,6 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="M10" dT="2025-06-02T08:55:10.82" personId="{0B063AB0-C045-794A-8C2E-DE2C142AB479}" id="{3F10DD45-61EC-6140-A23C-727EF741A4D9}">
-    <text>Volker Menze or Vince Bantu interview/Bantu book</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
@@ -2222,7 +2214,9 @@
         <f t="shared" si="5"/>
         <v>8-Kopten-und-Syrisch-Orthodoxen</v>
       </c>
-      <c r="M10" s="16"/>
+      <c r="M10" s="19" t="s">
+        <v>93</v>
+      </c>
       <c r="N10" t="s">
         <v>51</v>
       </c>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25christentum/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A78B6D9-8302-4147-82E5-82E6FE8C382B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{681B1894-69DC-7649-9282-BBACF8BB8637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -236,45 +236,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="K11" authorId="0" shapeId="0" xr:uid="{D73E6C6F-C73A-DC40-90D2-B0CA652CEFEF}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Microsoft Office User:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>St. Mark</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="95">
   <si>
     <t>blank</t>
   </si>
@@ -339,9 +306,6 @@
     <t>Einleitung</t>
   </si>
   <si>
-    <t>Exkursion</t>
-  </si>
-  <si>
     <t>Heilige Schriften, Schriftlichkeit/Mündlichkeit, sakrale Objekte</t>
   </si>
   <si>
@@ -373,9 +337,6 @@
   </si>
   <si>
     <t>Die Entfaltung der Gemeinden</t>
-  </si>
-  <si>
-    <t>Schlusswort</t>
   </si>
   <si>
     <t>Rückblick</t>
@@ -412,12 +373,6 @@
     <t>Den Heiligkeitsbegriff mit Beispielen erklären können.</t>
   </si>
   <si>
-    <t>Wie sieht eine Kirche aus?</t>
-  </si>
-  <si>
-    <t>Erfahren, wie in einer nicht-westlichen Tradition einen Gottesdienst gefeiert wird.</t>
-  </si>
-  <si>
     <t>Einige Bereiche nennen können, in denen der langjährige Austausch zwischen islamischen und ostkirchlichen Gemeinschaften besonders bedeutsam war.</t>
   </si>
   <si>
@@ -436,9 +391,6 @@
     <t>Gemeinsamkeiten und Unterschiede zwischen Kopten und Syrisch-Orthodoxen auflisten.</t>
   </si>
   <si>
-    <t>Eckpunkte der armenischen und äthiopischen Selbstnarrativen erzählen können.</t>
-  </si>
-  <si>
     <t>Wichtige Ereignisse auf eine Zeitleiste platzieren.</t>
   </si>
   <si>
@@ -463,9 +415,6 @@
     <t>Kopten und Syrisch-Orthodoxen</t>
   </si>
   <si>
-    <t>Armenier und Äthiopier</t>
-  </si>
-  <si>
     <t>Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (I)</t>
   </si>
   <si>
@@ -541,9 +490,6 @@
     <t>tamckeIslamUndChristentum2008</t>
   </si>
   <si>
-    <t>coptic-incense.jpg</t>
-  </si>
-  <si>
     <t>coptic-michael.jpg</t>
   </si>
   <si>
@@ -557,6 +503,30 @@
   </si>
   <si>
     <t>bantuFirstChristiansAfrica2020</t>
+  </si>
+  <si>
+    <t>Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (III)</t>
+  </si>
+  <si>
+    <t>Äthiopier und Nubier</t>
+  </si>
+  <si>
+    <t>Armenier und Georgier</t>
+  </si>
+  <si>
+    <t>Eckpunkte der armenischen Selbstnarrative erzählen können.</t>
+  </si>
+  <si>
+    <t>Eckpunkte der äthiopischer Selbstnarrative erzählen können.</t>
+  </si>
+  <si>
+    <t>Zusammenfassung</t>
+  </si>
+  <si>
+    <t>ethiopic-bl-add-ms-59874.jpg</t>
+  </si>
+  <si>
+    <t>evansArmeniansTheirMiddle2018, merianInventionArmenianAlphabet2018</t>
   </si>
 </sst>
 </file>
@@ -568,9 +538,16 @@
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="166" formatCode="dd\.mm"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -678,18 +655,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -699,26 +676,27 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -736,10 +714,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1070,7 +1044,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>14</v>
@@ -1097,7 +1071,7 @@
         <v>10</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>11</v>
@@ -1106,19 +1080,19 @@
         <v>12</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1136,7 +1110,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>19</v>
@@ -1151,14 +1125,14 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="L2" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B2 &amp; ". " &amp; F2,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>1-Einführung-Zielsetzung</v>
       </c>
       <c r="N2" s="17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="P2" t="str">
         <f t="shared" ref="P2:P14" si="2">"["&amp;B2&amp;"]"</f>
@@ -1288,16 +1262,16 @@
         <v>2025-05-05-2.md</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I3" t="str">
         <f t="shared" ref="I3:I14" si="4">B3 &amp; ". " &amp; F3 &amp; ": " &amp; G3</f>
@@ -1308,20 +1282,20 @@
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="L3" t="str">
         <f t="shared" ref="L3:L14" si="5">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B3 &amp; ". " &amp; F3,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>2-Heilige-Schriften-und-die-apostolische-Tradition</v>
       </c>
       <c r="M3" s="18" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="N3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P3" t="str">
         <f t="shared" si="2"/>
@@ -1446,16 +1420,16 @@
         <v>2025-05-12-3.md</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I4" t="str">
         <f t="shared" si="4"/>
@@ -1466,20 +1440,20 @@
         <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="L4" t="str">
         <f t="shared" si="5"/>
         <v>3-Abendmahl,-Pessach-und-Ostern</v>
       </c>
       <c r="M4" s="16" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="N4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="P4" t="str">
         <f t="shared" si="2"/>
@@ -1577,16 +1551,16 @@
         <v>2025-05-19-4.md</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I5" t="str">
         <f t="shared" si="4"/>
@@ -1597,20 +1571,20 @@
         <v>4</v>
       </c>
       <c r="K5" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="L5" t="str">
         <f t="shared" si="5"/>
         <v>4-Orthodoxie-und-Häresie</v>
       </c>
       <c r="M5" s="16" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="N5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="O5" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="P5" t="str">
         <f t="shared" si="2"/>
@@ -1708,16 +1682,16 @@
         <v>2025-05-26-5.md</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I6" t="str">
         <f t="shared" si="4"/>
@@ -1728,20 +1702,20 @@
         <v>5</v>
       </c>
       <c r="K6" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="L6" t="str">
         <f t="shared" si="5"/>
         <v>5-Askese,-Martyrium,-Wunder-und-Wallfahrt</v>
       </c>
       <c r="M6" s="16" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="N6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O6" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="P6" t="str">
         <f t="shared" si="2"/>
@@ -1839,13 +1813,13 @@
         <v>2025-06-02-6.md</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G7" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="4"/>
@@ -1856,20 +1830,20 @@
         <v>6</v>
       </c>
       <c r="K7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="L7" t="str">
         <f t="shared" si="5"/>
         <v>6-Begegnungen-mit-dem-Islam</v>
       </c>
       <c r="M7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="N7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="O7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="P7" t="str">
         <f t="shared" si="2"/>
@@ -2055,13 +2029,13 @@
         <v>2025-06-16-7.md</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G9" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="I9" t="str">
         <f t="shared" si="4"/>
@@ -2072,20 +2046,20 @@
         <v>7</v>
       </c>
       <c r="K9" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L9" t="str">
         <f t="shared" si="5"/>
         <v>7-Kirche-des-Ostens-(ostsyrisch/assyrianisch)</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="N9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="O9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="P9" t="str">
         <f t="shared" si="2"/>
@@ -2191,13 +2165,13 @@
         <v>2025-06-23-8.md</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G10" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="I10" t="str">
         <f t="shared" si="4"/>
@@ -2208,20 +2182,20 @@
         <v>8</v>
       </c>
       <c r="K10" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L10" t="str">
         <f t="shared" si="5"/>
         <v>8-Kopten-und-Syrisch-Orthodoxen</v>
       </c>
       <c r="M10" s="19" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="N10" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="O10" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="P10" t="str">
         <f t="shared" si="2"/>
@@ -2285,7 +2259,7 @@
 ## Lektüre
 ## Diskussion
 ## Vorschau
-Wie sieht eine Kirche aus?</v>
+Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (II)</v>
       </c>
       <c r="V10" t="str">
         <f t="shared" si="10"/>
@@ -2314,7 +2288,7 @@
 ## Lektüre
 ## Diskussion
 ## Vorschau
-Wie sieht eine Kirche aus?</v>
+Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (II)</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2329,32 +2303,37 @@
         <v>2025-06-30-9.md</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="G11" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I11" t="str">
         <f t="shared" si="4"/>
-        <v>9. Exkursion: Wie sieht eine Kirche aus?</v>
+        <v>9. Armenier und Georgier: Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (II)</v>
       </c>
       <c r="J11" s="3">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="K11" t="s">
-        <v>88</v>
+      <c r="K11" s="10" t="s">
+        <v>66</v>
       </c>
       <c r="L11" t="str">
         <f t="shared" si="5"/>
-        <v>9-Exkursion</v>
-      </c>
-      <c r="M11" s="16"/>
+        <v>9-Armenier-und-Georgier</v>
+      </c>
+      <c r="M11" s="20" t="s">
+        <v>94</v>
+      </c>
       <c r="N11" t="s">
-        <v>46</v>
+        <v>90</v>
+      </c>
+      <c r="O11" t="s">
+        <v>49</v>
       </c>
       <c r="P11" t="str">
         <f t="shared" si="2"/>
@@ -2377,13 +2356,13 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">---
 layout: reveal
-title: 'Wie sieht eine Kirche aus?'
+title: 'Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (II)'
 author: 'Nathan Gibson'
 session: 9
 tags: [9,slides]
 category: slides
-image: coptic-incense.jpg
-parallaxBackgroundImage: 'assets/img/coptic-incense.jpg'
+image: armenian-bell.jpg
+parallaxBackgroundImage: 'assets/img/armenian-bell.jpg'
 ---
 </v>
       </c>
@@ -2391,7 +2370,7 @@
         <f t="shared" si="8"/>
         <v># Einführung ins Christentum
 {: .r-fit-text}
-### Wie sieht eine Kirche aus?
+### Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (II)
 Sommersemester 2025
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
@@ -2400,7 +2379,7 @@
 ## Projekt
 ## Einleitung
 ## Heutiges Lernziel
-Erfahren, wie in einer nicht-westlichen Tradition einen Gottesdienst gefeiert wird.</v>
+Eckpunkte der armenischen Selbstnarrative erzählen können.</v>
       </c>
       <c r="U11" t="str">
         <f t="shared" si="9"/>
@@ -2414,17 +2393,17 @@
         <f t="shared" si="10"/>
         <v xml:space="preserve">---
 layout: reveal
-title: 'Wie sieht eine Kirche aus?'
+title: 'Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (II)'
 author: 'Nathan Gibson'
 session: 9
 tags: [9,slides]
 category: slides
-image: coptic-incense.jpg
-parallaxBackgroundImage: 'assets/img/coptic-incense.jpg'
+image: armenian-bell.jpg
+parallaxBackgroundImage: 'assets/img/armenian-bell.jpg'
 ---
 # Einführung ins Christentum
 {: .r-fit-text}
-### Wie sieht eine Kirche aus?
+### Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (II)
 Sommersemester 2025
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
@@ -2433,7 +2412,7 @@
 ## Projekt
 ## Einleitung
 ## Heutiges Lernziel
-Erfahren, wie in einer nicht-westlichen Tradition einen Gottesdienst gefeiert wird.
+Eckpunkte der armenischen Selbstnarrative erzählen können.
 ## Lektüre
 ## Diskussion
 ## Vorschau
@@ -2484,7 +2463,7 @@
 Sommersemester 2025
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-Erfahren, wie in einer nicht-westlichen Tradition einen Gottesdienst gefeiert wird.
+Eckpunkte der armenischen Selbstnarrative erzählen können.
 ## 📈 Rückblick: 
 ## Projekt
 ## Einleitung
@@ -2497,7 +2476,7 @@
 ## Lektüre
 ## Diskussion
 ## Vorschau
-Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (II)</v>
+Was haben wir gelernt?</v>
       </c>
       <c r="V12" t="str">
         <f t="shared" si="10"/>
@@ -2517,7 +2496,7 @@
 Sommersemester 2025
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-Erfahren, wie in einer nicht-westlichen Tradition einen Gottesdienst gefeiert wird.
+Eckpunkte der armenischen Selbstnarrative erzählen können.
 ## 📈 Rückblick: 
 ## Projekt
 ## Einleitung
@@ -2525,7 +2504,7 @@
 ## Lektüre
 ## Diskussion
 ## Vorschau
-Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (II)</v>
+Was haben wir gelernt?</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2540,35 +2519,35 @@
         <v>2025-07-14-10.md</v>
       </c>
       <c r="E13" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="G13" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="4"/>
-        <v>10. Armenier und Äthiopier: Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (II)</v>
+        <v>10. Rückblick: Was haben wir gelernt?</v>
       </c>
       <c r="J13" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="K13" s="10" t="s">
-        <v>72</v>
+      <c r="K13" t="s">
+        <v>84</v>
       </c>
       <c r="L13" t="str">
         <f t="shared" si="5"/>
-        <v>10-Armenier-und-Äthiopier</v>
+        <v>10-Rückblick</v>
       </c>
       <c r="M13" s="16"/>
       <c r="N13" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O13" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="P13" t="str">
         <f t="shared" si="2"/>
@@ -2591,21 +2570,21 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">---
 layout: reveal
-title: 'Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (II)'
+title: 'Was haben wir gelernt?'
 author: 'Nathan Gibson'
 session: 10
 tags: [10,slides]
 category: slides
-image: armenian-bell.jpg
-parallaxBackgroundImage: 'assets/img/armenian-bell.jpg'
+image: wadi-qelt.jpg
+parallaxBackgroundImage: 'assets/img/wadi-qelt.jpg'
 ---
 </v>
       </c>
       <c r="T13" t="str">
         <f t="shared" si="8"/>
-        <v># Einführung ins Christentum
+        <v xml:space="preserve"># Einführung ins Christentum
 {: .r-fit-text}
-### Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (II)
+### Was haben wir gelernt?
 Sommersemester 2025
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
@@ -2613,7 +2592,7 @@
 ## Projekt
 ## Einleitung
 ## Heutiges Lernziel
-Eckpunkte der armenischen und äthiopischen Selbstnarrativen erzählen können.</v>
+Über die Kursinhalte reflektieren und das eingeworbene Wissen für sich versichern. </v>
       </c>
       <c r="U13" t="str">
         <f t="shared" si="9"/>
@@ -2621,23 +2600,23 @@
 ## Lektüre
 ## Diskussion
 ## Vorschau
-Was haben wir gelernt?</v>
+Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (III)</v>
       </c>
       <c r="V13" t="str">
         <f t="shared" si="10"/>
         <v>---
 layout: reveal
-title: 'Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (II)'
+title: 'Was haben wir gelernt?'
 author: 'Nathan Gibson'
 session: 10
 tags: [10,slides]
 category: slides
-image: armenian-bell.jpg
-parallaxBackgroundImage: 'assets/img/armenian-bell.jpg'
+image: wadi-qelt.jpg
+parallaxBackgroundImage: 'assets/img/wadi-qelt.jpg'
 ---
 # Einführung ins Christentum
 {: .r-fit-text}
-### Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (II)
+### Was haben wir gelernt?
 Sommersemester 2025
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
@@ -2645,11 +2624,11 @@
 ## Projekt
 ## Einleitung
 ## Heutiges Lernziel
-Eckpunkte der armenischen und äthiopischen Selbstnarrativen erzählen können.
+Über die Kursinhalte reflektieren und das eingeworbene Wissen für sich versichern. 
 ## Lektüre
 ## Diskussion
 ## Vorschau
-Was haben wir gelernt?</v>
+Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (III)</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2664,35 +2643,35 @@
         <v>2025-07-21-11.md</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="G14" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="I14" t="str">
         <f t="shared" si="4"/>
-        <v>11. Rückblick: Was haben wir gelernt?</v>
+        <v>11. Äthiopier und Nubier: Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (III)</v>
       </c>
       <c r="J14" s="3">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="K14" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L14" t="str">
         <f t="shared" si="5"/>
-        <v>11-Rückblick</v>
+        <v>11-Äthiopier-und-Nubier</v>
       </c>
       <c r="M14" s="9"/>
       <c r="N14" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="O14" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="P14" t="str">
         <f t="shared" si="2"/>
@@ -2715,30 +2694,30 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">---
 layout: reveal
-title: 'Was haben wir gelernt?'
+title: 'Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (III)'
 author: 'Nathan Gibson'
 session: 11
 tags: [11,slides]
 category: slides
-image: wadi-qelt.jpg
-parallaxBackgroundImage: 'assets/img/wadi-qelt.jpg'
+image: ethiopic-bl-add-ms-59874.jpg
+parallaxBackgroundImage: 'assets/img/ethiopic-bl-add-ms-59874.jpg'
 ---
 </v>
       </c>
       <c r="T14" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve"># Einführung ins Christentum
+        <v># Einführung ins Christentum
 {: .r-fit-text}
-### Was haben wir gelernt?
+### Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (III)
 Sommersemester 2025
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-Eckpunkte der armenischen und äthiopischen Selbstnarrativen erzählen können.
+Über die Kursinhalte reflektieren und das eingeworbene Wissen für sich versichern. 
 ## 📈 Rückblick: 
 ## Projekt
 ## Einleitung
 ## Heutiges Lernziel
-Über die Kursinhalte reflektieren und das eingeworbene Wissen für sich versichern. </v>
+Eckpunkte der äthiopischer Selbstnarrative erzählen können.</v>
       </c>
       <c r="U14" t="str">
         <f t="shared" si="9"/>
@@ -2752,26 +2731,26 @@
         <f t="shared" si="10"/>
         <v xml:space="preserve">---
 layout: reveal
-title: 'Was haben wir gelernt?'
+title: 'Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (III)'
 author: 'Nathan Gibson'
 session: 11
 tags: [11,slides]
 category: slides
-image: wadi-qelt.jpg
-parallaxBackgroundImage: 'assets/img/wadi-qelt.jpg'
+image: ethiopic-bl-add-ms-59874.jpg
+parallaxBackgroundImage: 'assets/img/ethiopic-bl-add-ms-59874.jpg'
 ---
 # Einführung ins Christentum
 {: .r-fit-text}
-### Was haben wir gelernt?
+### Wie entwickelte sich die Kirche außerhalb des Römischen Reiches? (III)
 Sommersemester 2025
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-Eckpunkte der armenischen und äthiopischen Selbstnarrativen erzählen können.
+Über die Kursinhalte reflektieren und das eingeworbene Wissen für sich versichern. 
 ## 📈 Rückblick: 
 ## Projekt
 ## Einleitung
 ## Heutiges Lernziel
-Über die Kursinhalte reflektieren und das eingeworbene Wissen für sich versichern. 
+Eckpunkte der äthiopischer Selbstnarrative erzählen können.
 ## Lektüre
 ## Diskussion
 ## Vorschau

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25christentum/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{681B1894-69DC-7649-9282-BBACF8BB8637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE07A8E-1BAC-424D-B28E-FF1F525EB853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
